--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 01:46:10</t>
+          <t>2026-05-26 03:56:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 03:56:23</t>
+          <t>2026-05-26 06:06:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -875,212 +875,212 @@
         <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>600</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="I3" t="n">
         <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="J4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 06:06:28</t>
+          <t>2026-05-26 08:17:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -860,16 +860,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,22 +881,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="R2" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 08:17:38</t>
+          <t>2026-05-26 10:28:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>FC Yantra</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="H3" t="n">
-        <v>1.96</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.96</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>420</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>660</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,2276 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 10:28:44</t>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Finnish Ykkonen</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FC Jazz</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SalPa</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Finnish Ykkonen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>JJK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OLS</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Polish I Liga</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wieczysta Krakow</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Polonia Warszawa</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Polish I Liga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LKS Lodz</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ismaily</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pharco FC</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>El Geish</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SE Palmeiras</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sporting Cristal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:40:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -860,13 +860,13 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
         <v>1.04</v>
@@ -884,7 +884,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
@@ -899,10 +899,10 @@
         <v>1.43</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
         <v>2.6</v>
       </c>
       <c r="X3" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
         <v>23</v>
@@ -1180,7 +1180,7 @@
         <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
         <v>34</v>
@@ -1192,7 +1192,7 @@
         <v>9.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>32</v>
@@ -1201,7 +1201,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AK3" t="n">
         <v>22</v>
@@ -1213,64 +1213,64 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
@@ -1282,59 +1282,59 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BN3" t="n">
         <v>3.95</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
         <v>4.4</v>
@@ -1407,7 +1407,7 @@
         <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
         <v>1.01</v>
@@ -1416,7 +1416,7 @@
         <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
         <v>9.199999999999999</v>
@@ -1485,7 +1485,7 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU4" t="n">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BJ4" t="n">
         <v>15</v>
@@ -1542,25 +1542,25 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO4" t="n">
         <v>3.65</v>
       </c>
       <c r="BP4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BT4" t="n">
         <v>8.6</v>
@@ -1572,23 +1572,23 @@
         <v>48</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
@@ -1631,7 +1631,7 @@
         <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>1.96</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1646,7 +1646,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>660</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.37</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -2638,109 +2638,109 @@
         <v>1.88</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="H9" t="n">
         <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>1.58</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2755,25 +2755,25 @@
         <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
         <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
         <v>1.01</v>
@@ -2791,16 +2791,16 @@
         <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2815,10 +2815,10 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2836,7 +2836,7 @@
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -2898,13 +2898,13 @@
         <v>2.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>2.92</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
         <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
         <v>2.78</v>
@@ -3161,212 +3161,212 @@
         <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="n">
         <v>2.8</v>
@@ -3415,212 +3415,212 @@
         <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P12" t="n">
         <v>1.48</v>
       </c>
       <c r="Q12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH12" t="n">
         <v>2.68</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 12:40:03</t>
+          <t>2026-05-26 14:51:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
         <v>1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1129,34 +1129,34 @@
         <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
         <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1189,13 +1189,13 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1207,7 +1207,7 @@
         <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1222,40 +1222,40 @@
         <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AV3" t="n">
         <v>5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AZ3" t="n">
         <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC3" t="n">
         <v>4.6</v>
@@ -1264,13 +1264,13 @@
         <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH3" t="n">
         <v>3.35</v>
@@ -1282,59 +1282,59 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
         <v>5.8</v>
       </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.82</v>
+        <v>1.24</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.82</v>
+        <v>1.22</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1374,16 +1374,16 @@
         <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
         <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
@@ -1628,13 +1628,13 @@
         <v>1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
         <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.37</v>
@@ -1924,7 +1924,7 @@
         <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
         <v>1.99</v>
@@ -2139,7 +2139,7 @@
         <v>2.22</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
@@ -2178,7 +2178,7 @@
         <v>1.81</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
         <v>36</v>
@@ -2238,7 +2238,7 @@
         <v>3.85</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
         <v>3.6</v>
@@ -2262,7 +2262,7 @@
         <v>3.85</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
         <v>2.8</v>
@@ -2393,13 +2393,13 @@
         <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
@@ -2408,7 +2408,7 @@
         <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
         <v>2.68</v>
@@ -2423,73 +2423,73 @@
         <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="V8" t="n">
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG8" t="n">
         <v>15</v>
       </c>
-      <c r="AD8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>38</v>
       </c>
-      <c r="AF8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>44</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.01</v>
@@ -2498,13 +2498,13 @@
         <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
         <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
         <v>1.01</v>
@@ -2519,7 +2519,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
@@ -2534,7 +2534,7 @@
         <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2552,13 +2552,13 @@
         <v>8.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN8" t="n">
         <v>6</v>
@@ -2570,13 +2570,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
         <v>22</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
         <v>6.8</v>
@@ -2588,23 +2588,23 @@
         <v>19.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
         <v>14</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
@@ -2737,7 +2737,7 @@
         <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
         <v>44</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2892,13 @@
         <v>3.35</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H10" t="n">
         <v>2.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2907,212 +2907,212 @@
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>2.92</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="H11" t="n">
         <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
         <v>2.78</v>
@@ -3173,7 +3173,7 @@
         <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Q11" t="n">
         <v>2.88</v>
@@ -3191,10 +3191,10 @@
         <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
         <v>8.6</v>
@@ -3224,7 +3224,7 @@
         <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AH11" t="n">
         <v>29</v>
@@ -3260,7 +3260,7 @@
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
         <v>6.4</v>
@@ -3272,7 +3272,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX11" t="n">
         <v>14.5</v>
@@ -3284,25 +3284,25 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>48</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="n">
         <v>2.62</v>
@@ -3314,13 +3314,13 @@
         <v>12.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
@@ -3332,13 +3332,13 @@
         <v>32</v>
       </c>
       <c r="BQ11" t="n">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11" t="n">
         <v>5.9</v>
@@ -3350,23 +3350,23 @@
         <v>30</v>
       </c>
       <c r="BW11" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
         <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>46</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
         <v>2.8</v>
@@ -3421,31 +3421,31 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
         <v>1.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T12" t="n">
         <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
         <v>1.54</v>
@@ -3454,31 +3454,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE12" t="n">
         <v>70</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>28</v>
@@ -3493,10 +3493,10 @@
         <v>46</v>
       </c>
       <c r="AL12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN12" t="n">
         <v>55</v>
@@ -3508,13 +3508,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -3523,58 +3523,58 @@
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
         <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
         <v>2.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BN12" t="n">
         <v>5.5</v>
@@ -3586,13 +3586,13 @@
         <v>25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>36</v>
+        <v>9.4</v>
       </c>
       <c r="BT12" t="n">
         <v>6.6</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>26</v>
+        <v>8.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>44</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>40</v>
+        <v>9.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:51:10</t>
+          <t>2026-05-26 17:01:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -860,19 +860,19 @@
         <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
         <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
         <v>1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1111,55 +1111,55 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H3" t="n">
         <v>6.8</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
         <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T3" t="n">
         <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>2.6</v>
@@ -1219,82 +1219,82 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD3" t="n">
         <v>5.6</v>
       </c>
-      <c r="AX3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
         <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>2.34</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1306,35 +1306,35 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.31</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.22</v>
+        <v>1.89</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>2.16</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
         <v>1.92</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="J6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
         <v>1.37</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1921,7 +1921,7 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
         <v>1.99</v>
@@ -2142,7 +2142,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.21</v>
@@ -2256,7 +2256,7 @@
         <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AX7" t="n">
         <v>3.85</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
         <v>2.8</v>
@@ -2393,7 +2393,7 @@
         <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
@@ -2432,7 +2432,7 @@
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
         <v>36</v>
@@ -2459,7 +2459,7 @@
         <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
         <v>15</v>
@@ -2489,58 +2489,58 @@
         <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH8" t="n">
         <v>4.8</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G9" t="n">
         <v>2.08</v>
@@ -2659,10 +2659,10 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
         <v>2.24</v>
@@ -2680,7 +2680,7 @@
         <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
         <v>1.29</v>
@@ -2719,7 +2719,7 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
@@ -2764,7 +2764,7 @@
         <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2970,7 +2970,7 @@
         <v>30</v>
       </c>
       <c r="AG10" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>24</v>
@@ -3000,13 +3000,13 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT10" t="n">
         <v>9.4</v>
@@ -3015,13 +3015,13 @@
         <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.4</v>
+        <v>3.45</v>
       </c>
       <c r="AW10" t="n">
         <v>18.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>17.5</v>
+        <v>3.95</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
@@ -3030,22 +3030,22 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG10" t="n">
         <v>14.5</v>
@@ -3060,13 +3060,13 @@
         <v>10</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>7</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT10" t="n">
         <v>5.3</v>
@@ -3096,23 +3096,23 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>2.92</v>
       </c>
       <c r="G11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="H11" t="n">
         <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
         <v>2.78</v>
@@ -3170,7 +3170,7 @@
         <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P11" t="n">
         <v>1.43</v>
@@ -3185,16 +3185,16 @@
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
         <v>8.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 17:01:23</t>
+          <t>2026-05-26 19:11:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1111,103 +1111,103 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I3" t="n">
         <v>6.8</v>
       </c>
-      <c r="I3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.42</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF3" t="n">
         <v>970</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1216,91 +1216,91 @@
         <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP3" t="n">
         <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
         <v>5.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="AX3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD3" t="n">
         <v>3.65</v>
       </c>
-      <c r="AY3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="BF3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG3" t="n">
         <v>3.85</v>
       </c>
-      <c r="BG3" t="n">
-        <v>6</v>
-      </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,29 +1312,29 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.17</v>
+        <v>1.77</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1530,28 +1530,28 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="BJ4" t="n">
         <v>15</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="BN4" t="n">
         <v>6.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>1.33</v>
       </c>
       <c r="BP4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
         <v>1.68</v>
@@ -1560,35 +1560,35 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="BT4" t="n">
         <v>8.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
         <v>48</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>1.96</v>
       </c>
       <c r="I5" t="n">
         <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.92</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>660</v>
+        <v>970</v>
       </c>
       <c r="J6" t="n">
         <v>1.03</v>
@@ -1912,7 +1912,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>1.99</v>
@@ -2151,19 +2151,19 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="Q7" t="n">
         <v>1.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
         <v>2.08</v>
@@ -2178,10 +2178,10 @@
         <v>1.81</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
@@ -2196,7 +2196,7 @@
         <v>27</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -2223,7 +2223,7 @@
         <v>40</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
         <v>65</v>
@@ -2235,19 +2235,19 @@
         <v>10.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AU7" t="n">
         <v>8</v>
@@ -2259,34 +2259,34 @@
         <v>3.65</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC7" t="n">
         <v>3.8</v>
       </c>
-      <c r="BB7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="n">
         <v>970</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2390,10 +2390,10 @@
         <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
@@ -2432,7 +2432,7 @@
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="X8" t="n">
         <v>36</v>
@@ -2459,7 +2459,7 @@
         <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG8" t="n">
         <v>15</v>
@@ -2489,58 +2489,58 @@
         <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AX8" t="n">
         <v>3.6</v>
       </c>
       <c r="AY8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>3.4</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BA8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BB8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE8" t="n">
         <v>3.95</v>
       </c>
-      <c r="BC8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BH8" t="n">
         <v>4.8</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2659,25 +2659,25 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
         <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
         <v>2.3</v>
@@ -2686,10 +2686,10 @@
         <v>1.29</v>
       </c>
       <c r="W9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
@@ -2698,7 +2698,7 @@
         <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB9" t="n">
         <v>970</v>
@@ -2713,7 +2713,7 @@
         <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
@@ -2725,7 +2725,7 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK9" t="n">
         <v>23</v>
@@ -2740,13 +2740,13 @@
         <v>970</v>
       </c>
       <c r="AO9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
         <v>1.01</v>
@@ -2758,13 +2758,13 @@
         <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
         <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
         <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
         <v>1.01</v>
@@ -2791,7 +2791,7 @@
         <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
@@ -2836,7 +2836,7 @@
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
         <v>3.9</v>
@@ -2898,7 +2898,7 @@
         <v>2.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2919,7 +2919,7 @@
         <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
@@ -2937,7 +2937,7 @@
         <v>1.99</v>
       </c>
       <c r="V10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
         <v>1.34</v>
@@ -2949,7 +2949,7 @@
         <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
         <v>38</v>
@@ -2976,7 +2976,7 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
         <v>75</v>
@@ -2994,16 +2994,16 @@
         <v>60</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AS10" t="n">
         <v>4.1</v>
@@ -3015,16 +3015,16 @@
         <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AW10" t="n">
         <v>18.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
@@ -3033,19 +3033,19 @@
         <v>4.2</v>
       </c>
       <c r="BB10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
         <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
         <v>14.5</v>
@@ -3072,13 +3072,13 @@
         <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
@@ -3090,13 +3090,13 @@
         <v>5.3</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G11" t="n">
         <v>3.35</v>
@@ -3212,7 +3212,7 @@
         <v>9.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>17</v>
@@ -3245,7 +3245,7 @@
         <v>260</v>
       </c>
       <c r="AN11" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO11" t="n">
         <v>75</v>
@@ -3260,7 +3260,7 @@
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT11" t="n">
         <v>6.4</v>
@@ -3272,7 +3272,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
         <v>14.5</v>
@@ -3284,25 +3284,25 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="n">
         <v>2.62</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
         <v>2.46</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P12" t="n">
         <v>1.48</v>
@@ -3454,46 +3454,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
         <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>70</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
         <v>230</v>
@@ -3502,7 +3502,7 @@
         <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="n">
         <v>6.2</v>
@@ -3517,7 +3517,7 @@
         <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6</v>
@@ -3547,19 +3547,19 @@
         <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
         <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG12" t="n">
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI12" t="n">
         <v>2.22</v>
@@ -3568,7 +3568,7 @@
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,37 +3580,37 @@
         <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP12" t="n">
         <v>25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12" t="n">
         <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 19:11:26</t>
+          <t>2026-05-26 21:21:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
         <v>6.8</v>
@@ -1129,7 +1129,7 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
         <v>2.58</v>
@@ -1374,7 +1374,7 @@
         <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>2.92</v>
@@ -1383,16 +1383,16 @@
         <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
         <v>1.5</v>
@@ -1401,194 +1401,194 @@
         <v>2.68</v>
       </c>
       <c r="R4" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
         <v>1.63</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG4" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AH4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="BE4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP4" t="n">
         <v>22</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="BQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT4" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV4" t="n">
+      <c r="BU4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW4" t="n">
         <v>11</v>
       </c>
-      <c r="AW4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.65</v>
+        <v>12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.64</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>970</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>970</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.21</v>
@@ -2160,13 +2160,13 @@
         <v>2.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R7" t="n">
         <v>1.7</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.48</v>
@@ -2175,10 +2175,10 @@
         <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
         <v>38</v>
@@ -2214,7 +2214,7 @@
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ7" t="n">
         <v>70</v>
@@ -2223,7 +2223,7 @@
         <v>40</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
         <v>65</v>
@@ -2238,13 +2238,13 @@
         <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="AR7" t="n">
         <v>3.55</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AT7" t="n">
         <v>3.65</v>
@@ -2256,28 +2256,28 @@
         <v>8.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AX7" t="n">
         <v>3.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AZ7" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="BA7" t="n">
         <v>3.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
         <v>3.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE7" t="n">
         <v>3.95</v>
@@ -2289,7 +2289,7 @@
         <v>6.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>970</v>
+        <v>5</v>
       </c>
       <c r="BI7" t="n">
         <v>3.7</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="H8" t="n">
         <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2683,10 +2683,10 @@
         <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
         <v>27</v>
@@ -2695,13 +2695,13 @@
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
         <v>95</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
         <v>970</v>
@@ -2713,19 +2713,19 @@
         <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
         <v>23</v>
@@ -2740,7 +2740,7 @@
         <v>970</v>
       </c>
       <c r="AO9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2749,7 +2749,7 @@
         <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
         <v>1.01</v>
@@ -2758,13 +2758,13 @@
         <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
         <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
         <v>1.01</v>
@@ -2794,7 +2794,7 @@
         <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="n">
         <v>4.2</v>
@@ -2815,10 +2815,10 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G10" t="n">
         <v>3.9</v>
@@ -2904,25 +2904,25 @@
         <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
         <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
@@ -2931,10 +2931,10 @@
         <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
         <v>1.73</v>
@@ -2943,7 +2943,7 @@
         <v>1.34</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
         <v>11</v>
@@ -2952,13 +2952,13 @@
         <v>16</v>
       </c>
       <c r="AA10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB10" t="n">
         <v>15.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
         <v>14</v>
@@ -2973,7 +2973,7 @@
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>48</v>
@@ -3000,28 +3000,28 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.4</v>
+        <v>3.95</v>
       </c>
       <c r="AU10" t="n">
         <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AW10" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
@@ -3030,43 +3030,43 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>14.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.45</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10" t="n">
         <v>10</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
         <v>7</v>
@@ -3078,13 +3078,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
         <v>5.3</v>
@@ -3096,7 +3096,7 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -3200,16 +3200,16 @@
         <v>8.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
@@ -3224,13 +3224,13 @@
         <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
         <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
         <v>70</v>
@@ -3260,7 +3260,7 @@
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
         <v>6.4</v>
@@ -3272,7 +3272,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
         <v>14.5</v>
@@ -3284,25 +3284,25 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH11" t="n">
         <v>2.62</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
         <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP12" t="n">
         <v>25</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Z13" t="n">
         <v>210</v>
@@ -3723,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE13" t="n">
         <v>470</v>
@@ -3777,7 +3777,7 @@
         <v>11.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
         <v>8.800000000000001</v>
@@ -3792,7 +3792,7 @@
         <v>32</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB13" t="n">
         <v>7.4</v>
@@ -3801,10 +3801,10 @@
         <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
         <v>4.3</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>
@@ -3938,13 +3938,13 @@
         <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
         <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T14" t="n">
         <v>2.08</v>
@@ -3956,13 +3956,13 @@
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X14" t="n">
         <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>70</v>
@@ -4037,7 +4037,7 @@
         <v>5</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
         <v>7.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-26 21:21:05</t>
+          <t>2026-05-26 23:30:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I3" t="n">
         <v>6.8</v>
@@ -1129,13 +1129,13 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
         <v>1.42</v>
@@ -1147,10 +1147,10 @@
         <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.1</v>
@@ -1171,22 +1171,22 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF3" t="n">
         <v>970</v>
@@ -1198,7 +1198,7 @@
         <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
@@ -1216,61 +1216,61 @@
         <v>970</v>
       </c>
       <c r="AO3" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4</v>
       </c>
-      <c r="AV3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG3" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
         <v>4.2</v>
@@ -1306,35 +1306,35 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>1.88</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>2.92</v>
@@ -1389,145 +1389,145 @@
         <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S4" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
         <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
         <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
         <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AW4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE4" t="n">
         <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BI4" t="n">
         <v>2.28</v>
@@ -1542,34 +1542,34 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU4" t="n">
         <v>5.1</v>
       </c>
-      <c r="BO4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BV4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
         <v>11</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>970</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G6" t="n">
         <v>970</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="I6" t="n">
         <v>970</v>
@@ -1924,7 +1924,7 @@
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
         <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I7" t="n">
         <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>4.8</v>
@@ -2151,31 +2151,31 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T7" t="n">
         <v>1.48</v>
       </c>
       <c r="U7" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W7" t="n">
         <v>1.36</v>
@@ -2196,7 +2196,7 @@
         <v>27</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -2250,10 +2250,10 @@
         <v>3.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.6</v>
+        <v>3.25</v>
       </c>
       <c r="AW7" t="n">
         <v>3.55</v>
@@ -2286,13 +2286,13 @@
         <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
         <v>5</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2325,10 +2325,10 @@
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2384,43 +2384,43 @@
         <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
         <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.22</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="T8" t="n">
         <v>1.48</v>
@@ -2471,7 +2471,7 @@
         <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
         <v>26</v>
@@ -2489,64 +2489,64 @@
         <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
         <v>3.6</v>
       </c>
-      <c r="AR8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>3.5</v>
       </c>
-      <c r="AU8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BA8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BB8" t="n">
         <v>3.85</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BH8" t="n">
         <v>4.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.4</v>
@@ -2558,13 +2558,13 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8" t="n">
         <v>6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
         <v>15.5</v>
@@ -2582,7 +2582,7 @@
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
         <v>19.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2665,7 +2665,7 @@
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
         <v>1.63</v>
@@ -2677,7 +2677,7 @@
         <v>2.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
         <v>2.3</v>
@@ -2701,7 +2701,7 @@
         <v>95</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
         <v>970</v>
@@ -2728,10 +2728,10 @@
         <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>90</v>
@@ -2740,7 +2740,7 @@
         <v>970</v>
       </c>
       <c r="AO9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2836,7 +2836,7 @@
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -2892,64 +2892,64 @@
         <v>3.45</v>
       </c>
       <c r="G10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="I10" t="n">
         <v>2.38</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
         <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.73</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
         <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA10" t="n">
         <v>34</v>
@@ -2961,7 +2961,7 @@
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
         <v>32</v>
@@ -2970,19 +2970,19 @@
         <v>30</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL10" t="n">
         <v>70</v>
@@ -3000,91 +3000,91 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AR10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
         <v>4</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AW10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.3</v>
       </c>
       <c r="BH10" t="n">
         <v>3.45</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>10</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
         <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT10" t="n">
         <v>5.3</v>
@@ -3096,7 +3096,7 @@
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.96</v>
       </c>
       <c r="G11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
         <v>2.82</v>
@@ -3158,37 +3158,37 @@
         <v>2.78</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
         <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="P11" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
         <v>1.45</v>
@@ -3197,10 +3197,10 @@
         <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z11" t="n">
         <v>19</v>
@@ -3215,10 +3215,10 @@
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
         <v>22</v>
@@ -3227,7 +3227,7 @@
         <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI11" t="n">
         <v>90</v>
@@ -3239,28 +3239,28 @@
         <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AN11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO11" t="n">
         <v>75</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR11" t="n">
         <v>13.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
         <v>6.4</v>
@@ -3272,7 +3272,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
         <v>14.5</v>
@@ -3284,37 +3284,37 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3338,7 +3338,7 @@
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT11" t="n">
         <v>5.9</v>
@@ -3353,7 +3353,7 @@
         <v>8</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
         <v>9.199999999999999</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.48</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
@@ -3421,10 +3421,10 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P12" t="n">
         <v>1.48</v>
@@ -3439,7 +3439,7 @@
         <v>5.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
         <v>1.73</v>
@@ -3448,10 +3448,10 @@
         <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="n">
         <v>10.5</v>
@@ -3463,7 +3463,7 @@
         <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC12" t="n">
         <v>7.4</v>
@@ -3472,13 +3472,13 @@
         <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
         <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
         <v>25</v>
@@ -3487,7 +3487,7 @@
         <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
         <v>42</v>
@@ -3499,13 +3499,13 @@
         <v>230</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO12" t="n">
         <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.4</v>
@@ -3559,16 +3559,16 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,37 +3580,37 @@
         <v>5.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP12" t="n">
         <v>25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT12" t="n">
         <v>6.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -3651,28 +3651,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="G13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="H13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="I13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>4.3</v>
@@ -3681,28 +3681,28 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R13" t="n">
         <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="X13" t="n">
         <v>24</v>
@@ -3711,7 +3711,7 @@
         <v>46</v>
       </c>
       <c r="Z13" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -3723,10 +3723,10 @@
         <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AE13" t="n">
-        <v>470</v>
+        <v>410</v>
       </c>
       <c r="AF13" t="n">
         <v>7.4</v>
@@ -3735,10 +3735,10 @@
         <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI13" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AJ13" t="n">
         <v>9.199999999999999</v>
@@ -3747,10 +3747,10 @@
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AN13" t="n">
         <v>5.2</v>
@@ -3762,13 +3762,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3777,10 +3777,10 @@
         <v>11.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
@@ -3792,7 +3792,7 @@
         <v>32</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB13" t="n">
         <v>7.4</v>
@@ -3804,13 +3804,13 @@
         <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>4.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3822,59 +3822,59 @@
         <v>15.5</v>
       </c>
       <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU13" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-26 23:30:35</t>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3935,13 +3935,13 @@
         <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
         <v>3.95</v>
@@ -3968,7 +3968,7 @@
         <v>70</v>
       </c>
       <c r="AA14" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AB14" t="n">
         <v>8</v>
@@ -3977,7 +3977,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE14" t="n">
         <v>150</v>
@@ -4010,7 +4010,7 @@
         <v>16.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP14" t="n">
         <v>8.6</v>
@@ -4055,16 +4055,16 @@
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH14" t="n">
         <v>3.2</v>
@@ -4073,19 +4073,19 @@
         <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO14" t="n">
         <v>3.15</v>
@@ -4094,41 +4094,549 @@
         <v>12.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
         <v>10.5</v>
       </c>
       <c r="BU14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-27 01:40:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Barcelona (ECU)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>190</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>440</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>540</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-27 01:40:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>300</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>5.4</v>
       </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
+      <c r="BR16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>8</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-05-26 23:30:35</t>
+      <c r="BT16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-27 01:40:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S3" t="n">
         <v>4.2</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1171,7 +1171,7 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1180,34 +1180,34 @@
         <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1219,70 +1219,70 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU3" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW3" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5</v>
       </c>
       <c r="AX3" t="n">
         <v>3.55</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
         <v>4</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,50 +1291,50 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1368,227 +1368,227 @@
         <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4" t="n">
         <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL4" t="n">
         <v>70</v>
       </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AM4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV4" t="n">
         <v>13</v>
       </c>
-      <c r="AH4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AW4" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BE4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF4" t="n">
         <v>10</v>
       </c>
-      <c r="BF4" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG4" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW4" t="n">
         <v>12</v>
       </c>
-      <c r="BT4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>11</v>
-      </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ4" t="n">
         <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="G5" t="n">
         <v>2.08</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="G6" t="n">
         <v>970</v>
       </c>
       <c r="H6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="I6" t="n">
         <v>970</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G7" t="n">
         <v>3.8</v>
@@ -2139,7 +2139,7 @@
         <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
         <v>4.8</v>
@@ -2151,31 +2151,31 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>1.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="Q7" t="n">
         <v>1.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S7" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U7" t="n">
         <v>2.66</v>
       </c>
       <c r="V7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
         <v>1.36</v>
@@ -2238,10 +2238,10 @@
         <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
         <v>3.75</v>
@@ -2250,10 +2250,10 @@
         <v>3.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="AW7" t="n">
         <v>3.55</v>
@@ -2262,10 +2262,10 @@
         <v>3.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.45</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>3.7</v>
@@ -2286,71 +2286,71 @@
         <v>3.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="n">
         <v>5</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BT7" t="n">
         <v>5.7</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
         <v>1.48</v>
       </c>
       <c r="U8" t="n">
-        <v>2.72</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X8" t="n">
         <v>36</v>
@@ -2471,82 +2471,82 @@
         <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE8" t="n">
         <v>3.9</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4</v>
-      </c>
       <c r="BF8" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BH8" t="n">
         <v>4.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
         <v>8.4</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="BN8" t="n">
         <v>6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
@@ -2650,7 +2650,7 @@
         <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.27</v>
@@ -2659,19 +2659,19 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
         <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
         <v>2.48</v>
@@ -2758,7 +2758,7 @@
         <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
@@ -2836,7 +2836,7 @@
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I10" t="n">
         <v>2.38</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2916,7 +2916,7 @@
         <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
         <v>1.83</v>
@@ -2964,7 +2964,7 @@
         <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
         <v>30</v>
@@ -2994,22 +2994,22 @@
         <v>60</v>
       </c>
       <c r="AO10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU10" t="n">
         <v>6.6</v>
@@ -3021,7 +3021,7 @@
         <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
@@ -3030,22 +3030,22 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG10" t="n">
         <v>4.6</v>
@@ -3054,25 +3054,25 @@
         <v>3.45</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="BJ10" t="n">
         <v>970</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
@@ -3084,7 +3084,7 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT10" t="n">
         <v>5.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3149,55 +3149,55 @@
         <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J11" t="n">
         <v>2.78</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
         <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
         <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
         <v>8.199999999999999</v>
@@ -3239,13 +3239,13 @@
         <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM11" t="n">
         <v>240</v>
       </c>
       <c r="AN11" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
         <v>75</v>
@@ -3272,7 +3272,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
         <v>14.5</v>
@@ -3284,16 +3284,16 @@
         <v>19</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
         <v>6.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
         <v>7.4</v>
@@ -3305,10 +3305,10 @@
         <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
@@ -3335,7 +3335,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS11" t="n">
         <v>9.4</v>
@@ -3353,20 +3353,20 @@
         <v>8</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA11" t="n">
         <v>9.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
@@ -3409,52 +3409,52 @@
         <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
         <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V12" t="n">
         <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X12" t="n">
         <v>9</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
@@ -3490,22 +3490,22 @@
         <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN12" t="n">
         <v>48</v>
       </c>
       <c r="AO12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.4</v>
@@ -3559,22 +3559,22 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN12" t="n">
         <v>5.5</v>
@@ -3586,13 +3586,13 @@
         <v>25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12" t="n">
         <v>6.6</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>14.5</v>
       </c>
       <c r="I13" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="J13" t="n">
         <v>6</v>
@@ -3672,7 +3672,7 @@
         <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
         <v>4.3</v>
@@ -3684,19 +3684,19 @@
         <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
         <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
@@ -3723,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="AD13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AE13" t="n">
         <v>410</v>
@@ -3741,7 +3741,7 @@
         <v>290</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AK13" t="n">
         <v>16.5</v>
@@ -3762,13 +3762,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3777,10 +3777,10 @@
         <v>11.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
@@ -3792,7 +3792,7 @@
         <v>32</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB13" t="n">
         <v>7.4</v>
@@ -3804,13 +3804,13 @@
         <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
         <v>4.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3822,59 +3822,59 @@
         <v>15.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BO13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BP13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BT13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -3935,10 +3935,10 @@
         <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -4162,22 +4162,22 @@
         <v>1.29</v>
       </c>
       <c r="G15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="I15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -4189,10 +4189,10 @@
         <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
@@ -4201,16 +4201,16 @@
         <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
         <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X15" t="n">
         <v>20</v>
@@ -4228,13 +4228,13 @@
         <v>7.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AF15" t="n">
         <v>7</v>
@@ -4243,10 +4243,10 @@
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AI15" t="n">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="AJ15" t="n">
         <v>9.199999999999999</v>
@@ -4255,10 +4255,10 @@
         <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
-        <v>540</v>
+        <v>440</v>
       </c>
       <c r="AN15" t="n">
         <v>6.4</v>
@@ -4270,13 +4270,13 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>5.9</v>
@@ -4285,22 +4285,22 @@
         <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.8</v>
+        <v>40</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="n">
         <v>7.8</v>
@@ -4309,80 +4309,80 @@
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>5.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.89</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.76</v>
+        <v>6.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.89</v>
+        <v>10.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="BP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA15" t="n">
         <v>10</v>
       </c>
-      <c r="BQ15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>29</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>20</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.73</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
@@ -4443,7 +4443,7 @@
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
         <v>2.08</v>
@@ -4461,7 +4461,7 @@
         <v>1.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
         <v>3.1</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 01:40:28</t>
+          <t>2026-05-27 03:50:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q2" t="n">
         <v>1.43</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.64</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I3" t="n">
         <v>8.4</v>
@@ -1126,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
@@ -1135,13 +1135,13 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
         <v>2.12</v>
@@ -1282,19 +1282,19 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="BN3" t="n">
         <v>3.95</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
         <v>3.2</v>
@@ -1386,40 +1386,40 @@
         <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O4" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
         <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y4" t="n">
         <v>10</v>
@@ -1428,10 +1428,10 @@
         <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
         <v>7.2</v>
@@ -1452,7 +1452,7 @@
         <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
@@ -1461,91 +1461,91 @@
         <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
         <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BG4" t="n">
         <v>10</v>
       </c>
-      <c r="BC4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH4" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>16.5</v>
+        <v>2.26</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
         <v>4</v>
@@ -1554,13 +1554,13 @@
         <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.5</v>
+        <v>2.18</v>
       </c>
       <c r="BT4" t="n">
         <v>6.8</v>
@@ -1569,33 +1569,33 @@
         <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>12</v>
+        <v>2.16</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="BZ4" t="n">
         <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>13.5</v>
+        <v>2.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,246 +1610,246 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.24</v>
+        <v>2.92</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.43</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.92</v>
-      </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,174 +1859,174 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.22</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>970</v>
+        <v>2.88</v>
       </c>
       <c r="H6" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>970</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2035,75 +2035,75 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SalPa</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>970</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="T7" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="X7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JJK</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OLS</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>970</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>1.28</v>
       </c>
       <c r="I8" t="n">
-        <v>3.05</v>
+        <v>970</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>1.32</v>
       </c>
       <c r="O8" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>2.72</v>
+        <v>1.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.67</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,94 +2626,94 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>SalPa</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>3.05</v>
       </c>
       <c r="G9" t="n">
-        <v>1.98</v>
+        <v>3.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.95</v>
+        <v>1.94</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Y9" t="n">
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
@@ -2722,150 +2722,150 @@
         <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>3.65</v>
       </c>
       <c r="BG9" t="n">
-        <v>26</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BI9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>3.15</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>JJK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>2.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE10" t="n">
         <v>34</v>
       </c>
-      <c r="AB10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>60</v>
-      </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="AQ10" t="n">
         <v>3.55</v>
       </c>
       <c r="AR10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO10" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS10" t="n">
         <v>8.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.96</v>
+        <v>1.81</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>1.97</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1.63</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.92</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
-        <v>6.4</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
       </c>
       <c r="AF11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK11" t="n">
         <v>22</v>
       </c>
-      <c r="AG11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>60</v>
-      </c>
       <c r="AL11" t="n">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>970</v>
       </c>
       <c r="AO11" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF11" t="n">
-        <v>7</v>
-      </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.18</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,192 +3383,192 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74</v>
+        <v>3.95</v>
       </c>
       <c r="H12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.4</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.56</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL12" t="n">
         <v>70</v>
       </c>
       <c r="AM12" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AO12" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="AP12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU12" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6</v>
-      </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.24</v>
+        <v>2.96</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,50 +3577,50 @@
         <v>10</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -3654,25 +3654,25 @@
         <v>1.26</v>
       </c>
       <c r="G13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="n">
         <v>1.31</v>
       </c>
-      <c r="H13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.32</v>
-      </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
         <v>4.3</v>
@@ -3684,34 +3684,34 @@
         <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R13" t="n">
         <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X13" t="n">
         <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Z13" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -3720,13 +3720,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AE13" t="n">
-        <v>410</v>
+        <v>360</v>
       </c>
       <c r="AF13" t="n">
         <v>7.4</v>
@@ -3735,10 +3735,10 @@
         <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI13" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AJ13" t="n">
         <v>9.6</v>
@@ -3750,7 +3750,7 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AN13" t="n">
         <v>5.2</v>
@@ -3762,13 +3762,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3777,10 +3777,10 @@
         <v>11.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
@@ -3789,28 +3789,28 @@
         <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
         <v>12</v>
       </c>
       <c r="BD13" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="n">
         <v>4.2</v>
@@ -3822,59 +3822,59 @@
         <v>15.5</v>
       </c>
       <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU13" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
         <v>1.75</v>
@@ -3926,7 +3926,7 @@
         <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
@@ -3938,13 +3938,13 @@
         <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
         <v>2.08</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="G15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="J15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -4189,10 +4189,10 @@
         <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
@@ -4201,16 +4201,16 @@
         <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V15" t="n">
         <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="X15" t="n">
         <v>20</v>
@@ -4225,28 +4225,28 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AD15" t="n">
         <v>65</v>
       </c>
       <c r="AE15" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AG15" t="n">
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AI15" t="n">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="AJ15" t="n">
         <v>9.199999999999999</v>
@@ -4255,10 +4255,10 @@
         <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM15" t="n">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="AN15" t="n">
         <v>6.4</v>
@@ -4267,7 +4267,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>7.2</v>
@@ -4279,55 +4279,55 @@
         <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="AW15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BA15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG15" t="n">
         <v>9</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BK15" t="n">
         <v>6.6</v>
@@ -4339,28 +4339,28 @@
         <v>10.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="BP15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BR15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BU15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4378,11 +4378,11 @@
         <v>14.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G16" t="n">
         <v>1.48</v>
       </c>
       <c r="H16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.42</v>
@@ -4449,7 +4449,7 @@
         <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
         <v>3.85</v>
@@ -4464,7 +4464,7 @@
         <v>1.09</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X16" t="n">
         <v>14.5</v>
@@ -4473,7 +4473,7 @@
         <v>32</v>
       </c>
       <c r="Z16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -4485,13 +4485,13 @@
         <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE16" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AF16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -4500,7 +4500,7 @@
         <v>36</v>
       </c>
       <c r="AI16" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AJ16" t="n">
         <v>12</v>
@@ -4512,7 +4512,7 @@
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AN16" t="n">
         <v>9.199999999999999</v>
@@ -4527,10 +4527,10 @@
         <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT16" t="n">
         <v>5.5</v>
@@ -4539,7 +4539,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW16" t="n">
         <v>9.199999999999999</v>
@@ -4554,7 +4554,7 @@
         <v>7.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB16" t="n">
         <v>9</v>
@@ -4572,7 +4572,7 @@
         <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="n">
         <v>3.35</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 03:50:21</t>
+          <t>2026-05-27 06:00:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.34</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.34</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>990</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>1.27</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
         <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1171,43 +1171,43 @@
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
@@ -1219,122 +1219,122 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.5</v>
       </c>
       <c r="AR3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW3" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AX3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY3" t="n">
+      <c r="BD3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN3" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.68</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -1365,187 +1365,187 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
         <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
         <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS4" t="n">
         <v>5.1</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10</v>
-      </c>
       <c r="BB4" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
         <v>4</v>
@@ -1554,13 +1554,13 @@
         <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.18</v>
+        <v>12.5</v>
       </c>
       <c r="BT4" t="n">
         <v>6.8</v>
@@ -1569,26 +1569,26 @@
         <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.2</v>
+        <v>14</v>
       </c>
       <c r="BZ4" t="n">
         <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.2</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -1625,58 +1625,58 @@
         <v>3.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K5" t="n">
         <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="n">
         <v>21</v>
@@ -1685,109 +1685,109 @@
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN5" t="n">
         <v>90</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>75</v>
-      </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR5" t="n">
         <v>13.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV5" t="n">
         <v>11</v>
       </c>
       <c r="AW5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AX5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF5" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
         <v>5.9</v>
@@ -1799,7 +1799,7 @@
         <v>11</v>
       </c>
       <c r="BN5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
         <v>4.6</v>
@@ -1811,7 +1811,7 @@
         <v>8.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS5" t="n">
         <v>9.6</v>
@@ -1820,29 +1820,29 @@
         <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
         <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1897,7 +1897,7 @@
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O6" t="n">
         <v>1.56</v>
@@ -1906,7 +1906,7 @@
         <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1921,25 +1921,25 @@
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
         <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
         <v>10</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>7.4</v>
@@ -1948,37 +1948,37 @@
         <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
         <v>17.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
         <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
         <v>220</v>
       </c>
       <c r="AN6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
         <v>6.4</v>
@@ -1987,28 +1987,28 @@
         <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>18</v>
@@ -2035,7 +2035,7 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI6" t="n">
         <v>2.24</v>
@@ -2044,31 +2044,31 @@
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
         <v>6.6</v>
@@ -2080,23 +2080,23 @@
         <v>36</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -2118,184 +2118,184 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I7" t="n">
-        <v>970</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S7" t="n">
-        <v>1.43</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="W7" t="n">
-        <v>1.92</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
         <v>1.01</v>
@@ -2307,50 +2307,50 @@
         <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO7" t="n">
         <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ7" t="n">
         <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS7" t="n">
         <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU7" t="n">
         <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW7" t="n">
         <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA7" t="n">
         <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -2367,33 +2367,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>970</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>1.28</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
         <v>970</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SalPa</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.05</v>
+        <v>1.28</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>970</v>
       </c>
       <c r="H9" t="n">
-        <v>1.94</v>
+        <v>1.31</v>
       </c>
       <c r="I9" t="n">
-        <v>2.14</v>
+        <v>970</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O9" t="n">
         <v>1.02</v>
       </c>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.15</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,184 +2880,184 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JJK</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OLS</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH10" t="n">
         <v>3.45</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X10" t="n">
-        <v>36</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BI10" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ10" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BK10" t="n">
         <v>5.2</v>
@@ -3066,60 +3066,60 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BR10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>8</v>
       </c>
-      <c r="BX10" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>9</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,94 +3134,94 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>SalPa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97</v>
+        <v>3.9</v>
       </c>
       <c r="H11" t="n">
-        <v>3.95</v>
+        <v>1.98</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.9</v>
       </c>
       <c r="W11" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Y11" t="n">
         <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
         <v>970</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG11" t="n">
         <v>970</v>
@@ -3230,150 +3230,150 @@
         <v>970</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AN11" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AU11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,184 +3388,184 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>JJK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="G12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X12" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE12" t="n">
         <v>3.95</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="BF12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG12" t="n">
         <v>11</v>
       </c>
-      <c r="Z12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BH12" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="BJ12" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="BK12" t="n">
         <v>5.2</v>
@@ -3574,60 +3574,60 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA12" t="n">
         <v>7</v>
       </c>
-      <c r="BO12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K13" t="n">
+        <v>950</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.26</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.3</v>
       </c>
       <c r="O13" t="n">
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="Y14" t="n">
         <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD14" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>240</v>
+        <v>48</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY14" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BO14" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BP14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -4145,78 +4145,78 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I15" t="n">
         <v>18.5</v>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
         <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="n">
         <v>190</v>
@@ -4225,164 +4225,164 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AF15" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG15" t="n">
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI15" t="n">
-        <v>420</v>
+        <v>280</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AK15" t="n">
         <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>470</v>
+        <v>310</v>
       </c>
       <c r="AN15" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU15" t="n">
         <v>11.5</v>
       </c>
       <c r="AV15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW15" t="n">
         <v>8</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY15" t="n">
         <v>9</v>
       </c>
-      <c r="AX15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE15" t="n">
         <v>8</v>
       </c>
-      <c r="BE15" t="n">
-        <v>9</v>
-      </c>
       <c r="BF15" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BK15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU15" t="n">
         <v>6.6</v>
       </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 06:00:13</t>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>
@@ -4399,244 +4399,752 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="G16" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="I16" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
         <v>4.2</v>
       </c>
-      <c r="K16" t="n">
-        <v>4.9</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="X16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>32</v>
       </c>
-      <c r="Z16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>270</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>36</v>
-      </c>
       <c r="AI16" t="n">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7</v>
-      </c>
       <c r="BG16" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BK16" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BP16" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BR16" t="n">
         <v>34</v>
       </c>
       <c r="BS16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="BZ16" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Barcelona (ECU)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H17" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>440</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>460</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X18" t="n">
         <v>14</v>
       </c>
-      <c r="BU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
+      <c r="Y18" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>12.5</v>
       </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY16" t="n">
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
         <v>12.5</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="BN18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ18" t="n">
         <v>20</v>
       </c>
-      <c r="CA16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-05-27 06:00:13</t>
+      <c r="CA18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:10:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Kyzyl-Zhar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Zhetysu</t>
+          <t>FK Aktobe</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.92</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.84</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX2" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AY2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AZ2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="BA2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR2" t="n">
         <v>42</v>
       </c>
-      <c r="AK2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS2" t="n">
-        <v>1.23</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.23</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>FK Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Yantra</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
         <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.58</v>
+        <v>1.8</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
       </c>
       <c r="Z3" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
         <v>970</v>
       </c>
-      <c r="AD3" t="n">
-        <v>36</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.76</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>3.95</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.16</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>FK Atyrau</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>2.48</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="O4" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AA4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>110</v>
       </c>
-      <c r="AB4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AK4" t="n">
         <v>70</v>
       </c>
-      <c r="AF4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AL4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO4" t="n">
         <v>28</v>
       </c>
-      <c r="AI4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>120</v>
-      </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>FC Yantra</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
         <v>9</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK5" t="n">
         <v>21</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AL5" t="n">
         <v>65</v>
       </c>
-      <c r="AB5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY5" t="n">
         <v>8</v>
       </c>
-      <c r="AD5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="AZ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA5" t="n">
         <v>5.7</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BC5" t="n">
         <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>1.71</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="BV5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
         <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.800000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -1864,246 +1864,246 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N6" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="X6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX6" t="n">
         <v>65</v>
       </c>
-      <c r="AF6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG6" t="n">
+      <c r="BY6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="CA6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>9</v>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,246 +2118,246 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FK Kaisar</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elimai FC</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AK7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM7" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
         <v>90</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.45</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.96</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.35</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,169 +2372,169 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Kaspyi Aktau</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>970</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.43</v>
+        <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2543,68 +2543,68 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Ordabasy</t>
+          <t>FK Kaisar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat Almaty</t>
+          <t>Elimai FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.28</v>
+        <v>3.7</v>
       </c>
       <c r="G9" t="n">
-        <v>970</v>
+        <v>5.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>970</v>
+        <v>2.12</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
         <v>1.02</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chrobry Glogow</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>FK Kaspyi Aktau</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="G10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.95</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.16</v>
-      </c>
       <c r="I10" t="n">
-        <v>2.42</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG10" t="n">
         <v>11.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>19</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
       </c>
       <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
         <v>50</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>70</v>
-      </c>
       <c r="AM10" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
         <v>8.4</v>
       </c>
-      <c r="AW10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BU10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Ykkonen</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,244 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Jazz</t>
+          <t>FC Ordabasy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SalPa</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="G11" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.1</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.45</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="X11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>38</v>
       </c>
-      <c r="Y11" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AK11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN11" t="n">
         <v>30</v>
       </c>
-      <c r="AB11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>25</v>
-      </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.7</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JJK</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OLS</t>
+          <t>SalPa</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.28</v>
+        <v>3.35</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>3.95</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>1.97</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>1.21</v>
@@ -3424,210 +3424,210 @@
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R12" t="n">
         <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.48</v>
       </c>
       <c r="U12" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y12" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AB12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AC12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW12" t="n">
         <v>13</v>
       </c>
-      <c r="AD12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>19</v>
-      </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>3.85</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>3.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>19</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>3.65</v>
       </c>
       <c r="BG12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BI12" t="n">
         <v>3.7</v>
       </c>
       <c r="BJ12" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>11.5</v>
+        <v>2.34</v>
       </c>
       <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
         <v>6</v>
       </c>
-      <c r="BO12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>8</v>
-      </c>
       <c r="BX12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BZ12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,244 +3637,244 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>JJK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>1.26</v>
+        <v>2.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>Chrobry Glogow</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>2.36</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG14" t="n">
         <v>970</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>970</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO14" t="n">
         <v>5.1</v>
       </c>
-      <c r="BO14" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="n">
-        <v>1.32</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="J15" t="n">
-        <v>5.9</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>1.24</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,244 +4399,244 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="G16" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="H16" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="Y16" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AM16" t="n">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
         <v>13</v>
       </c>
-      <c r="AR16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AW16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY16" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK16" t="n">
         <v>4.9</v>
       </c>
-      <c r="BH16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="BP16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>19.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -4653,244 +4653,244 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="I17" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="J17" t="n">
         <v>5.9</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Z17" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AE17" t="n">
         <v>440</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL17" t="n">
         <v>55</v>
       </c>
-      <c r="AI17" t="n">
-        <v>320</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>65</v>
-      </c>
       <c r="AM17" t="n">
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="AN17" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX17" t="n">
         <v>6</v>
       </c>
-      <c r="AT17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV17" t="n">
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>5.5</v>
       </c>
-      <c r="AW17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>16</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BP17" t="n">
+      <c r="BR17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS17" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
         <v>18.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 08:10:09</t>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>
@@ -4907,192 +4907,192 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="H18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="I18" t="n">
+      <c r="BG18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>12</v>
       </c>
-      <c r="J18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>290</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX18" t="n">
+      <c r="BK18" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>6.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5101,34 +5101,34 @@
         <v>12.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BP18" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
         <v>34</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
@@ -5137,14 +5137,522 @@
         <v>11.5</v>
       </c>
       <c r="BZ18" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:20:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Barcelona (ECU)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4</v>
+      </c>
+      <c r="X19" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>430</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:20:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>20</v>
       </c>
-      <c r="CA18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-05-27 08:10:09</t>
+      <c r="CA20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:20:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -887,7 +887,7 @@
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
         <v>2.14</v>
@@ -899,16 +899,16 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
         <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
         <v>13</v>
@@ -923,7 +923,7 @@
         <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.4</v>
@@ -935,10 +935,10 @@
         <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
@@ -947,10 +947,10 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
         <v>60</v>
@@ -959,34 +959,34 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO2" t="n">
         <v>44</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2" t="n">
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX2" t="n">
         <v>13.5</v>
@@ -998,25 +998,25 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="n">
         <v>3.2</v>
@@ -1034,43 +1034,43 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>5.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
         <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -1135,7 +1135,7 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
@@ -1144,7 +1144,7 @@
         <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1159,10 +1159,10 @@
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1177,10 +1177,10 @@
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
@@ -1201,7 +1201,7 @@
         <v>90</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK3" t="n">
         <v>32</v>
@@ -1225,10 +1225,10 @@
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1237,10 +1237,10 @@
         <v>5.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX3" t="n">
         <v>9.6</v>
@@ -1249,28 +1249,28 @@
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1282,16 +1282,16 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
         <v>3.6</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1389,55 +1389,55 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z4" t="n">
         <v>16</v>
       </c>
       <c r="AA4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>34</v>
@@ -1461,70 +1461,70 @@
         <v>70</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM4" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1643,16 +1643,16 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1661,16 +1661,16 @@
         <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
         <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1679,31 +1679,31 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC5" t="n">
         <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1712,7 +1712,7 @@
         <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>65</v>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR5" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT5" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AU5" t="n">
         <v>3.8</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AV5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE5" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH5" t="n">
         <v>3.2</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>2.26</v>
       </c>
       <c r="BN5" t="n">
         <v>3.9</v>
@@ -1814,35 +1814,35 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.6</v>
+        <v>2.24</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.16</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.36</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
         <v>3.7</v>
@@ -1885,7 +1885,7 @@
         <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
         <v>3.15</v>
@@ -1906,7 +1906,7 @@
         <v>1.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1933,28 +1933,28 @@
         <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
         <v>70</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>28</v>
@@ -1963,10 +1963,10 @@
         <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
@@ -1975,7 +1975,7 @@
         <v>230</v>
       </c>
       <c r="AN6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
         <v>120</v>
@@ -1984,16 +1984,16 @@
         <v>6.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>6.4</v>
@@ -2002,10 +2002,10 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="n">
         <v>2.64</v>
@@ -2044,7 +2044,7 @@
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2065,7 +2065,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
         <v>12.5</v>
@@ -2074,10 +2074,10 @@
         <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW6" t="n">
         <v>12</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
         <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.72</v>
@@ -2160,7 +2160,7 @@
         <v>1.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
         <v>1.15</v>
@@ -2175,16 +2175,16 @@
         <v>1.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>8.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
@@ -2229,13 +2229,13 @@
         <v>270</v>
       </c>
       <c r="AN7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="n">
         <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
@@ -2244,7 +2244,7 @@
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -2256,7 +2256,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
         <v>14.5</v>
@@ -2268,25 +2268,25 @@
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.58</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
         <v>3.3</v>
@@ -2396,7 +2396,7 @@
         <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.52</v>
@@ -2405,16 +2405,16 @@
         <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
@@ -2432,7 +2432,7 @@
         <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
         <v>9.6</v>
@@ -2456,7 +2456,7 @@
         <v>16.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
@@ -2468,13 +2468,13 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL8" t="n">
         <v>80</v>
@@ -2483,7 +2483,7 @@
         <v>220</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO8" t="n">
         <v>80</v>
@@ -2492,40 +2492,40 @@
         <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
         <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
         <v>1.01</v>
@@ -2537,7 +2537,7 @@
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
@@ -2552,7 +2552,7 @@
         <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2573,7 +2573,7 @@
         <v>7.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8" t="n">
         <v>8.800000000000001</v>
@@ -2582,7 +2582,7 @@
         <v>6.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
         <v>36</v>
@@ -2591,20 +2591,20 @@
         <v>8.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA8" t="n">
         <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -2635,97 +2635,97 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="G9" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="I9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
         <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AB9" t="n">
         <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
         <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="n">
         <v>65</v>
@@ -2734,131 +2734,131 @@
         <v>75</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH9" t="n">
         <v>3.45</v>
       </c>
-      <c r="AW9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BI9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.52</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR9" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="BV9" t="n">
         <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX9" t="n">
         <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.36</v>
+        <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.14</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.06</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="n">
         <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -3146,227 +3146,227 @@
         <v>2.24</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ11" t="n">
         <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT11" t="n">
         <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
         <v>32</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
         <v>3.95</v>
       </c>
       <c r="H12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
@@ -3430,13 +3430,13 @@
         <v>2.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="T12" t="n">
         <v>1.48</v>
@@ -3445,7 +3445,7 @@
         <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W12" t="n">
         <v>1.34</v>
@@ -3457,7 +3457,7 @@
         <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
         <v>30</v>
@@ -3502,10 +3502,10 @@
         <v>25</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ12" t="n">
         <v>11</v>
@@ -3514,10 +3514,10 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU12" t="n">
         <v>8.4</v>
@@ -3529,7 +3529,7 @@
         <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AY12" t="n">
         <v>12</v>
@@ -3538,25 +3538,25 @@
         <v>11</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BB12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD12" t="n">
         <v>4</v>
       </c>
-      <c r="BC12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH12" t="n">
         <v>5</v>
@@ -3568,31 +3568,31 @@
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>4.9</v>
       </c>
       <c r="BT12" t="n">
         <v>5.7</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -3654,16 +3654,16 @@
         <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H13" t="n">
         <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -3672,7 +3672,7 @@
         <v>1.21</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
         <v>6</v>
@@ -3684,13 +3684,13 @@
         <v>2.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R13" t="n">
         <v>1.7</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
         <v>1.48</v>
@@ -3771,7 +3771,7 @@
         <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
@@ -3783,7 +3783,7 @@
         <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
         <v>9.199999999999999</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>2.16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
@@ -3932,10 +3932,10 @@
         <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
         <v>1.94</v>
@@ -3953,28 +3953,28 @@
         <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W14" t="n">
         <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
         <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
         <v>13.5</v>
@@ -3989,7 +3989,7 @@
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>48</v>
@@ -4010,61 +4010,61 @@
         <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
         <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW14" t="n">
         <v>3.85</v>
       </c>
-      <c r="AW14" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG14" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>14</v>
       </c>
       <c r="BH14" t="n">
         <v>3.45</v>
@@ -4088,7 +4088,7 @@
         <v>7</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4106,10 +4106,10 @@
         <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW14" t="n">
         <v>6.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G15" t="n">
         <v>110</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I15" t="n">
         <v>970</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -4183,7 +4183,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O15" t="n">
         <v>1.24</v>
@@ -4207,10 +4207,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G16" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
         <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>4.6</v>
@@ -4440,19 +4440,19 @@
         <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
         <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
         <v>1.6</v>
@@ -4464,61 +4464,61 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
         <v>100</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
         <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
         <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP16" t="n">
         <v>1.03</v>
@@ -4539,13 +4539,13 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
         <v>7.6</v>
@@ -4554,13 +4554,13 @@
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>1.01</v>
@@ -4569,7 +4569,7 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
@@ -4578,7 +4578,7 @@
         <v>4.3</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4596,7 +4596,7 @@
         <v>5.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G17" t="n">
         <v>1.3</v>
       </c>
       <c r="H17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="I17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -4700,13 +4700,13 @@
         <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
         <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
         <v>2.38</v>
@@ -4718,13 +4718,13 @@
         <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z17" t="n">
         <v>200</v>
@@ -4733,16 +4733,16 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE17" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AF17" t="n">
         <v>7.4</v>
@@ -4751,7 +4751,7 @@
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="n">
         <v>310</v>
@@ -4763,13 +4763,13 @@
         <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
         <v>330</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -4778,37 +4778,37 @@
         <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS17" t="n">
         <v>9</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="AW17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>6</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB17" t="n">
         <v>7.6</v>
@@ -4817,16 +4817,16 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
         <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="n">
         <v>4.2</v>
@@ -4856,7 +4856,7 @@
         <v>7.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BR17" t="n">
         <v>28</v>
@@ -4886,11 +4886,11 @@
         <v>12</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -4921,31 +4921,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
         <v>7.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
         <v>1.41</v>
@@ -4957,13 +4957,13 @@
         <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
         <v>1.74</v>
@@ -4972,10 +4972,10 @@
         <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
         <v>22</v>
@@ -4987,10 +4987,10 @@
         <v>280</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
         <v>34</v>
@@ -4999,7 +4999,7 @@
         <v>150</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
@@ -5029,122 +5029,122 @@
         <v>240</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AQ18" t="n">
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="n">
         <v>3.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT18" t="n">
         <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BZ18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H19" t="n">
         <v>13</v>
       </c>
       <c r="I19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K19" t="n">
         <v>6.4</v>
@@ -5199,7 +5199,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
@@ -5226,7 +5226,7 @@
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X19" t="n">
         <v>21</v>
@@ -5244,7 +5244,7 @@
         <v>7.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD19" t="n">
         <v>65</v>
@@ -5271,7 +5271,7 @@
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM19" t="n">
         <v>450</v>
@@ -5286,13 +5286,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
         <v>5.9</v>
@@ -5301,10 +5301,10 @@
         <v>10.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19" t="n">
         <v>5.8</v>
@@ -5313,28 +5313,28 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB19" t="n">
         <v>7</v>
       </c>
-      <c r="BA19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
         <v>5.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH19" t="n">
         <v>3.8</v>
@@ -5358,13 +5358,13 @@
         <v>3.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="BP19" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR19" t="n">
         <v>32</v>
@@ -5394,11 +5394,11 @@
         <v>14.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.43</v>
       </c>
       <c r="G20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="n">
         <v>9.800000000000001</v>
@@ -5441,10 +5441,10 @@
         <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -5483,7 +5483,7 @@
         <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y20" t="n">
         <v>26</v>
@@ -5498,19 +5498,19 @@
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE20" t="n">
         <v>290</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>36</v>
@@ -5522,16 +5522,16 @@
         <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
         <v>320</v>
       </c>
       <c r="AN20" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -5540,55 +5540,55 @@
         <v>9.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR20" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT20" t="n">
         <v>5.7</v>
       </c>
       <c r="AU20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX20" t="n">
         <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF20" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>8</v>
-      </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="n">
         <v>3.3</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 10:20:06</t>
+          <t>2026-05-27 12:29:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H2" t="n">
         <v>2.84</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.82</v>
       </c>
       <c r="I2" t="n">
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -881,7 +881,7 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
@@ -953,7 +953,7 @@
         <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
@@ -974,19 +974,19 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX2" t="n">
         <v>13.5</v>
@@ -998,25 +998,25 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD2" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
         <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.98</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -1135,13 +1135,13 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
         <v>2.18</v>
@@ -1162,7 +1162,7 @@
         <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1225,19 +1225,19 @@
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
         <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
         <v>5.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
         <v>5.3</v>
@@ -1249,7 +1249,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BA3" t="n">
         <v>5.4</v>
@@ -1267,7 +1267,7 @@
         <v>5.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG3" t="n">
         <v>5.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
@@ -1410,10 +1410,10 @@
         <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W4" t="n">
         <v>1.3</v>
@@ -1449,7 +1449,7 @@
         <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>60</v>
@@ -1527,16 +1527,16 @@
         <v>18</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,10 +1545,10 @@
         <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
@@ -1563,13 +1563,13 @@
         <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.65</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>1.41</v>
@@ -1652,25 +1652,25 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1685,7 +1685,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>970</v>
@@ -1697,7 +1697,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1712,7 +1712,7 @@
         <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>65</v>
@@ -1730,55 +1730,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>2.38</v>
       </c>
       <c r="AT5" t="n">
         <v>5.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.1</v>
+        <v>2.38</v>
       </c>
       <c r="AX5" t="n">
         <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BB5" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BC5" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>2.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.2</v>
+        <v>2.38</v>
       </c>
       <c r="BH5" t="n">
         <v>3.2</v>
@@ -1790,59 +1790,59 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.16</v>
+        <v>7.4</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.24</v>
+        <v>5.1</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K6" t="n">
         <v>3.15</v>
@@ -1894,7 +1894,7 @@
         <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N6" t="n">
         <v>2.5</v>
@@ -1906,7 +1906,7 @@
         <v>1.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1927,7 +1927,7 @@
         <v>1.66</v>
       </c>
       <c r="X6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
@@ -1939,7 +1939,7 @@
         <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>7.2</v>
@@ -1972,7 +1972,7 @@
         <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN6" t="n">
         <v>40</v>
@@ -1987,22 +1987,22 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
@@ -2014,25 +2014,25 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8.6</v>
       </c>
       <c r="BH6" t="n">
         <v>2.64</v>
@@ -2074,7 +2074,7 @@
         <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV6" t="n">
         <v>38</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.25</v>
       </c>
       <c r="H7" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
         <v>3.1</v>
@@ -2157,7 +2157,7 @@
         <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" t="n">
         <v>2.9</v>
@@ -2217,7 +2217,7 @@
         <v>100</v>
       </c>
       <c r="AJ7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
         <v>65</v>
@@ -2250,7 +2250,7 @@
         <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2381,61 +2381,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="O8" t="n">
         <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y8" t="n">
         <v>10</v>
@@ -2447,10 +2447,10 @@
         <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD8" t="n">
         <v>16.5</v>
@@ -2468,22 +2468,22 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>220</v>
       </c>
       <c r="AN8" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
         <v>80</v>
@@ -2492,25 +2492,25 @@
         <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
@@ -2522,67 +2522,67 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>32</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>6.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
         <v>36</v>
@@ -2594,17 +2594,17 @@
         <v>60</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="CA8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="J9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.4</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG9" t="n">
         <v>17</v>
       </c>
-      <c r="Y9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>21</v>
-      </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
         <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AO9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX9" t="n">
         <v>16.5</v>
       </c>
-      <c r="AP9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP9" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY9" t="n">
         <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="CA9" t="n">
         <v>7.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -2889,40 +2889,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="G10" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
         <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
@@ -2934,25 +2934,25 @@
         <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
         <v>8</v>
@@ -2964,10 +2964,10 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2976,37 +2976,37 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO10" t="n">
         <v>110</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>130</v>
       </c>
       <c r="AP10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
         <v>6.2</v>
@@ -3015,10 +3015,10 @@
         <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -3027,10 +3027,10 @@
         <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
         <v>13.5</v>
@@ -3039,80 +3039,80 @@
         <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
       </c>
       <c r="BS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BT10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>8</v>
-      </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -3143,178 +3143,178 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
         <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
         <v>55</v>
       </c>
-      <c r="AF11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>70</v>
-      </c>
       <c r="AJ11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK11" t="n">
         <v>38</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AS11" t="n">
         <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
         <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE11" t="n">
         <v>4.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3323,40 +3323,40 @@
         <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS11" t="n">
         <v>8.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11" t="n">
         <v>34</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -3406,13 +3406,13 @@
         <v>1.94</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.21</v>
@@ -3427,13 +3427,13 @@
         <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S12" t="n">
         <v>2.14</v>
@@ -3445,7 +3445,7 @@
         <v>2.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W12" t="n">
         <v>1.34</v>
@@ -3514,7 +3514,7 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.8</v>
+        <v>17.5</v>
       </c>
       <c r="AT12" t="n">
         <v>3.8</v>
@@ -3535,7 +3535,7 @@
         <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
         <v>3.8</v>
@@ -3553,7 +3553,7 @@
         <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="BG12" t="n">
         <v>6.2</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="BN12" t="n">
         <v>7.8</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -3759,7 +3759,7 @@
         <v>18</v>
       </c>
       <c r="AP13" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
         <v>14</v>
@@ -3771,7 +3771,7 @@
         <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
@@ -3783,7 +3783,7 @@
         <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY13" t="n">
         <v>9.199999999999999</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -3908,22 +3908,22 @@
         <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="n">
         <v>2.16</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3935,10 +3935,10 @@
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
@@ -3953,7 +3953,7 @@
         <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
         <v>1.35</v>
@@ -3965,7 +3965,7 @@
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA14" t="n">
         <v>38</v>
@@ -4034,7 +4034,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX14" t="n">
         <v>18.5</v>
@@ -4046,7 +4046,7 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB14" t="n">
         <v>4.2</v>
@@ -4088,7 +4088,7 @@
         <v>7</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
@@ -4106,7 +4106,7 @@
         <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV14" t="n">
         <v>17.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -4159,118 +4159,118 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="G15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE15" t="n">
         <v>110</v>
       </c>
-      <c r="H15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="AF15" t="n">
         <v>970</v>
       </c>
-      <c r="J15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K15" t="n">
-        <v>950</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.01</v>
       </c>
-      <c r="M15" t="n">
+      <c r="AQ15" t="n">
         <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
         <v>1.03</v>
@@ -4279,37 +4279,37 @@
         <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
         <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
         <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
         <v>1.03</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.83</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
         <v>3.9</v>
@@ -4425,10 +4425,10 @@
         <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.26</v>
@@ -4440,31 +4440,31 @@
         <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
         <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R16" t="n">
         <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X16" t="n">
         <v>28</v>
@@ -4515,13 +4515,13 @@
         <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AO16" t="n">
         <v>38</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.03</v>
@@ -4533,10 +4533,10 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
         <v>12.5</v>
@@ -4545,10 +4545,10 @@
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
         <v>12</v>
@@ -4569,7 +4569,7 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -4682,13 +4682,13 @@
         <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
         <v>4.4</v>
@@ -4700,16 +4700,16 @@
         <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
         <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
         <v>1.6</v>
@@ -4724,7 +4724,7 @@
         <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Z17" t="n">
         <v>200</v>
@@ -4748,7 +4748,7 @@
         <v>7.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
         <v>44</v>
@@ -4763,7 +4763,7 @@
         <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>330</v>
@@ -4781,10 +4781,10 @@
         <v>32</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4793,10 +4793,10 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX17" t="n">
         <v>6</v>
@@ -4805,10 +4805,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB17" t="n">
         <v>7.6</v>
@@ -4817,16 +4817,16 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF17" t="n">
         <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH17" t="n">
         <v>4.2</v>
@@ -4850,7 +4850,7 @@
         <v>3.65</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="BP17" t="n">
         <v>7.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H18" t="n">
         <v>6.4</v>
@@ -4939,7 +4939,7 @@
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
@@ -4954,7 +4954,7 @@
         <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
@@ -4972,7 +4972,7 @@
         <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
         <v>11</v>
@@ -4987,7 +4987,7 @@
         <v>280</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>9.4</v>
@@ -5029,16 +5029,16 @@
         <v>240</v>
       </c>
       <c r="AP18" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
         <v>5.9</v>
@@ -5050,7 +5050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX18" t="n">
         <v>6.8</v>
@@ -5062,7 +5062,7 @@
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5071,19 +5071,19 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI18" t="n">
         <v>2.42</v>
@@ -5092,13 +5092,13 @@
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN18" t="n">
         <v>4.2</v>
@@ -5110,41 +5110,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT18" t="n">
         <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ18" t="n">
         <v>29</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -5190,16 +5190,16 @@
         <v>5.9</v>
       </c>
       <c r="K19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
@@ -5208,7 +5208,7 @@
         <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R19" t="n">
         <v>1.36</v>
@@ -5271,7 +5271,7 @@
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM19" t="n">
         <v>450</v>
@@ -5301,7 +5301,7 @@
         <v>10.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AW19" t="n">
         <v>8.199999999999999</v>
@@ -5319,7 +5319,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC19" t="n">
         <v>12.5</v>
@@ -5358,13 +5358,13 @@
         <v>3.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="BP19" t="n">
         <v>7.6</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR19" t="n">
         <v>32</v>
@@ -5394,11 +5394,11 @@
         <v>14.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -5453,40 +5453,40 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z20" t="n">
         <v>120</v>
@@ -5498,16 +5498,16 @@
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE20" t="n">
         <v>290</v>
       </c>
       <c r="AF20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -5522,7 +5522,7 @@
         <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
         <v>60</v>
@@ -5531,7 +5531,7 @@
         <v>320</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -5540,13 +5540,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>5.7</v>
@@ -5555,10 +5555,10 @@
         <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX20" t="n">
         <v>6.4</v>
@@ -5567,10 +5567,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
         <v>9.199999999999999</v>
@@ -5579,16 +5579,16 @@
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
         <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>3.3</v>
@@ -5612,7 +5612,7 @@
         <v>3.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="BP20" t="n">
         <v>9</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 12:29:40</t>
+          <t>2026-05-27 14:41:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -869,10 +869,10 @@
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
         <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
         <v>34</v>
@@ -1231,7 +1231,7 @@
         <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
         <v>5.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -1380,10 +1380,10 @@
         <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
@@ -1482,13 +1482,13 @@
         <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>8.4</v>
@@ -1506,13 +1506,13 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB4" t="n">
         <v>4.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
         <v>4.1</v>
@@ -1530,37 +1530,37 @@
         <v>3.05</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
         <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>5</v>
@@ -1572,13 +1572,13 @@
         <v>18</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
         <v>1.6</v>
@@ -1628,7 +1628,7 @@
         <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1637,34 +1637,34 @@
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -1679,7 +1679,7 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1688,7 +1688,7 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
         <v>32</v>
@@ -1730,119 +1730,119 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AX5" t="n">
         <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AZ5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>5.5</v>
       </c>
-      <c r="BA5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1897,16 +1897,16 @@
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,16 +1915,16 @@
         <v>5.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
         <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X6" t="n">
         <v>8.6</v>
@@ -1939,7 +1939,7 @@
         <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
         <v>7.2</v>
@@ -1987,22 +1987,22 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
@@ -2014,25 +2014,25 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF6" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="n">
         <v>2.64</v>
@@ -2056,19 +2056,19 @@
         <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
         <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
@@ -2077,10 +2077,10 @@
         <v>5.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
         <v>65</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K7" t="n">
         <v>3.05</v>
@@ -2250,7 +2250,7 @@
         <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -2259,7 +2259,7 @@
         <v>5.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -2381,37 +2381,37 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N8" t="n">
         <v>2.46</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
         <v>2.82</v>
@@ -2420,7 +2420,7 @@
         <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T8" t="n">
         <v>2.12</v>
@@ -2429,13 +2429,13 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
         <v>1.54</v>
       </c>
       <c r="X8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y8" t="n">
         <v>10</v>
@@ -2450,7 +2450,7 @@
         <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD8" t="n">
         <v>16.5</v>
@@ -2486,31 +2486,31 @@
         <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
@@ -2522,25 +2522,25 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB8" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>32</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
         <v>2.66</v>
@@ -2564,7 +2564,7 @@
         <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
         <v>26</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
         <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>1.36</v>
@@ -2683,10 +2683,10 @@
         <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
         <v>1.94</v>
@@ -2937,7 +2937,7 @@
         <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.89</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H11" t="n">
         <v>2.7</v>
@@ -3155,13 +3155,13 @@
         <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -3176,7 +3176,7 @@
         <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
         <v>1.29</v>
@@ -3194,7 +3194,7 @@
         <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
         <v>14.5</v>
@@ -3209,7 +3209,7 @@
         <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
@@ -3260,7 +3260,7 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -3272,7 +3272,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
         <v>13.5</v>
@@ -3284,31 +3284,31 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BC11" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
         <v>10</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
         <v>1.94</v>
@@ -3409,7 +3409,7 @@
         <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
         <v>4.9</v>
@@ -3436,7 +3436,7 @@
         <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T12" t="n">
         <v>1.48</v>
@@ -3448,7 +3448,7 @@
         <v>1.91</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
         <v>38</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -3765,19 +3765,19 @@
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
         <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
         <v>19</v>
@@ -3795,7 +3795,7 @@
         <v>21</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.8</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
         <v>15.5</v>
@@ -3807,7 +3807,7 @@
         <v>3.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -3911,16 +3911,16 @@
         <v>3.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I14" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
@@ -3929,31 +3929,31 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
         <v>1.96</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W14" t="n">
         <v>1.35</v>
@@ -3968,19 +3968,19 @@
         <v>17.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB14" t="n">
         <v>16.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF14" t="n">
         <v>32</v>
@@ -3989,10 +3989,10 @@
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
         <v>85</v>
@@ -4013,28 +4013,28 @@
         <v>23</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
         <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT14" t="n">
         <v>11</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AV14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX14" t="n">
         <v>18.5</v>
@@ -4046,22 +4046,22 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF14" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.1</v>
       </c>
       <c r="BG14" t="n">
         <v>13.5</v>
@@ -4070,7 +4070,7 @@
         <v>3.45</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ14" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4.9</v>
@@ -4183,7 +4183,7 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
@@ -4210,7 +4210,7 @@
         <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X15" t="n">
         <v>21</v>
@@ -4267,58 +4267,58 @@
         <v>120</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>1.83</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
         <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>4.4</v>
@@ -4440,7 +4440,7 @@
         <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
         <v>2.36</v>
@@ -4449,7 +4449,7 @@
         <v>1.61</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
         <v>2.5</v>
@@ -4464,10 +4464,10 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="X16" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4596,7 +4596,7 @@
         <v>5.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -4667,58 +4667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
         <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
         <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
         <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="X17" t="n">
         <v>22</v>
@@ -4727,7 +4727,7 @@
         <v>46</v>
       </c>
       <c r="Z17" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4736,13 +4736,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD17" t="n">
         <v>65</v>
       </c>
       <c r="AE17" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AF17" t="n">
         <v>7.4</v>
@@ -4751,10 +4751,10 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI17" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AJ17" t="n">
         <v>9.4</v>
@@ -4766,7 +4766,7 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN17" t="n">
         <v>5.3</v>
@@ -4781,10 +4781,10 @@
         <v>32</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4793,10 +4793,10 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>6</v>
@@ -4805,10 +4805,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
         <v>7.6</v>
@@ -4817,22 +4817,22 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF17" t="n">
         <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH17" t="n">
         <v>4.2</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
         <v>15.5</v>
@@ -4847,34 +4847,34 @@
         <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BP17" t="n">
         <v>7.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS17" t="n">
         <v>7.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>12</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
         <v>6.4</v>
@@ -4933,10 +4933,10 @@
         <v>7.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>1.55</v>
@@ -4945,7 +4945,7 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O18" t="n">
         <v>1.41</v>
@@ -4972,7 +4972,7 @@
         <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
         <v>11</v>
@@ -4999,7 +4999,7 @@
         <v>150</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
@@ -5029,16 +5029,16 @@
         <v>240</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
         <v>5.9</v>
@@ -5050,7 +5050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX18" t="n">
         <v>6.8</v>
@@ -5062,7 +5062,7 @@
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5071,16 +5071,16 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH18" t="n">
         <v>3</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -5178,16 +5178,16 @@
         <v>1.28</v>
       </c>
       <c r="G19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="J19" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K19" t="n">
         <v>6.6</v>
@@ -5199,37 +5199,37 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="R19" t="n">
         <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
         <v>4.1</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
         <v>38</v>
@@ -5244,13 +5244,13 @@
         <v>7.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AE19" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
         <v>7</v>
@@ -5259,19 +5259,19 @@
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI19" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK19" t="n">
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM19" t="n">
         <v>450</v>
@@ -5292,16 +5292,16 @@
         <v>8</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>5.9</v>
       </c>
       <c r="AU19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AW19" t="n">
         <v>8.199999999999999</v>
@@ -5316,7 +5316,7 @@
         <v>7.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
         <v>7.8</v>
@@ -5334,19 +5334,19 @@
         <v>5.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5355,28 +5355,28 @@
         <v>10.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BO19" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="BP19" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ19" t="n">
         <v>5.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BU19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G20" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
         <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -5462,7 +5462,7 @@
         <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
@@ -5471,7 +5471,7 @@
         <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
         <v>1.6</v>
@@ -5480,7 +5480,7 @@
         <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
@@ -5498,7 +5498,7 @@
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
         <v>44</v>
@@ -5510,7 +5510,7 @@
         <v>7.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
         <v>36</v>
@@ -5522,7 +5522,7 @@
         <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
         <v>60</v>
@@ -5543,10 +5543,10 @@
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT20" t="n">
         <v>5.7</v>
@@ -5558,19 +5558,19 @@
         <v>32</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX20" t="n">
         <v>6.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB20" t="n">
         <v>9.199999999999999</v>
@@ -5582,13 +5582,13 @@
         <v>8.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
         <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH20" t="n">
         <v>3.3</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:41:38</t>
+          <t>2026-05-27 16:54:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
         <v>2.82</v>
@@ -872,7 +872,7 @@
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.45</v>
@@ -881,7 +881,7 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
@@ -905,13 +905,13 @@
         <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
         <v>11.5</v>
@@ -920,49 +920,49 @@
         <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AO2" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>9</v>
@@ -974,7 +974,7 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -986,7 +986,7 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="AX2" t="n">
         <v>13.5</v>
@@ -995,28 +995,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
         <v>2.28</v>
@@ -1171,10 +1171,10 @@
         <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AA3" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>8.4</v>
@@ -1186,34 +1186,34 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AL3" t="n">
+        <v>350</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN3" t="n">
         <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>95</v>
@@ -1225,10 +1225,10 @@
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1240,7 +1240,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
         <v>9.6</v>
@@ -1249,28 +1249,28 @@
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1377,10 +1377,10 @@
         <v>2.36</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
         <v>1.41</v>
@@ -1407,7 +1407,7 @@
         <v>4.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>1.87</v>
@@ -1452,22 +1452,22 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL4" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AM4" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AO4" t="n">
         <v>30</v>
@@ -1482,7 +1482,7 @@
         <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
@@ -1506,22 +1506,22 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
         <v>18</v>
@@ -1554,7 +1554,7 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1569,10 +1569,10 @@
         <v>3.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
@@ -1640,7 +1640,7 @@
         <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
         <v>2.82</v>
@@ -1661,67 +1661,67 @@
         <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
         <v>2.62</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1730,55 +1730,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.42</v>
+        <v>7.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
         <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
         <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1790,7 +1790,7 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>3.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1900,7 +1900,7 @@
         <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
         <v>1.5</v>
@@ -1912,10 +1912,10 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
         <v>1.76</v>
@@ -1927,7 +1927,7 @@
         <v>1.64</v>
       </c>
       <c r="X6" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
@@ -1936,19 +1936,19 @@
         <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
         <v>7.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD6" t="n">
         <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1966,10 +1966,10 @@
         <v>38</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM6" t="n">
         <v>220</v>
@@ -1987,10 +1987,10 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -2002,7 +2002,7 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
@@ -2014,25 +2014,25 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="n">
         <v>2.64</v>
@@ -2056,7 +2056,7 @@
         <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>2.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
         <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
         <v>3.05</v>
@@ -2154,10 +2154,10 @@
         <v>2.36</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
         <v>2.9</v>
@@ -2169,7 +2169,7 @@
         <v>6.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
         <v>1.68</v>
@@ -2178,10 +2178,10 @@
         <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y7" t="n">
         <v>8.199999999999999</v>
@@ -2190,10 +2190,10 @@
         <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -2202,19 +2202,19 @@
         <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>100</v>
+        <v>460</v>
       </c>
       <c r="AJ7" t="n">
         <v>65</v>
@@ -2223,19 +2223,19 @@
         <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AM7" t="n">
         <v>270</v>
       </c>
       <c r="AN7" t="n">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AO7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.2</v>
@@ -2244,7 +2244,7 @@
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -2256,10 +2256,10 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="AY7" t="n">
         <v>11.5</v>
@@ -2268,31 +2268,31 @@
         <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,7 +2316,7 @@
         <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
@@ -2325,13 +2325,13 @@
         <v>9.6</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU7" t="n">
         <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW7" t="n">
         <v>8.199999999999999</v>
@@ -2340,17 +2340,17 @@
         <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>70</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2384,22 +2384,22 @@
         <v>2.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="K8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
@@ -2408,13 +2408,13 @@
         <v>2.46</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="P8" t="n">
         <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
@@ -2429,13 +2429,13 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y8" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
         <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
         <v>8</v>
@@ -2453,10 +2453,10 @@
         <v>6.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
@@ -2465,28 +2465,28 @@
         <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AM8" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>90</v>
+        <v>390</v>
       </c>
       <c r="AP8" t="n">
         <v>6.4</v>
@@ -2498,7 +2498,7 @@
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2510,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
@@ -2522,25 +2522,25 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB8" t="n">
         <v>9</v>
       </c>
-      <c r="BB8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
         <v>32</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="n">
         <v>2.66</v>
@@ -2564,13 +2564,13 @@
         <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP8" t="n">
         <v>26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BR8" t="n">
         <v>55</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.36</v>
@@ -2668,7 +2668,7 @@
         <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R9" t="n">
         <v>1.31</v>
@@ -2683,22 +2683,22 @@
         <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
         <v>15</v>
@@ -2710,10 +2710,10 @@
         <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG9" t="n">
         <v>17</v>
@@ -2722,10 +2722,10 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK9" t="n">
         <v>48</v>
@@ -2734,13 +2734,13 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>48</v>
       </c>
       <c r="AO9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP9" t="n">
         <v>9.6</v>
@@ -2752,13 +2752,13 @@
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
         <v>8.6</v>
@@ -2776,22 +2776,22 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BG9" t="n">
         <v>16</v>
@@ -2800,7 +2800,7 @@
         <v>3.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2812,34 +2812,34 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ9" t="n">
         <v>7.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS9" t="n">
         <v>8</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU9" t="n">
         <v>3.95</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW9" t="n">
         <v>6.4</v>
@@ -2848,7 +2848,7 @@
         <v>34</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>32</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
         <v>3.85</v>
@@ -2937,34 +2937,34 @@
         <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>8</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
@@ -2973,28 +2973,28 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
         <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="AP10" t="n">
         <v>9.199999999999999</v>
@@ -3003,10 +3003,10 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>6.2</v>
@@ -3018,7 +3018,7 @@
         <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
@@ -3030,7 +3030,7 @@
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
         <v>13.5</v>
@@ -3039,16 +3039,16 @@
         <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="n">
         <v>3.2</v>
@@ -3060,59 +3060,59 @@
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT10" t="n">
         <v>8.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA10" t="n">
         <v>7.4</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>7</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -3200,7 +3200,7 @@
         <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
         <v>22</v>
@@ -3209,7 +3209,7 @@
         <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
@@ -3233,7 +3233,7 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
         <v>38</v>
@@ -3245,10 +3245,10 @@
         <v>120</v>
       </c>
       <c r="AN11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO11" t="n">
         <v>36</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>38</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -3260,7 +3260,7 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -3272,7 +3272,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>13.5</v>
@@ -3284,31 +3284,31 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="BJ11" t="n">
         <v>10</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="H12" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.21</v>
@@ -3424,13 +3424,13 @@
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R12" t="n">
         <v>1.7</v>
@@ -3439,160 +3439,160 @@
         <v>2.16</v>
       </c>
       <c r="T12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="U12" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
       </c>
       <c r="Z12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD12" t="n">
         <v>20</v>
       </c>
-      <c r="AA12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AK12" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AL12" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI12" t="n">
         <v>3.7</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.66</v>
+        <v>5.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT12" t="n">
         <v>5.7</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
         <v>2.52</v>
@@ -3660,7 +3660,7 @@
         <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -3699,7 +3699,7 @@
         <v>2.74</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.66</v>
@@ -3711,7 +3711,7 @@
         <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
         <v>55</v>
@@ -3726,7 +3726,7 @@
         <v>17</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
         <v>25</v>
@@ -3759,25 +3759,25 @@
         <v>18</v>
       </c>
       <c r="AP13" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AU13" t="n">
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
         <v>19</v>
@@ -3795,7 +3795,7 @@
         <v>21</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BC13" t="n">
         <v>15.5</v>
@@ -3804,10 +3804,10 @@
         <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="I14" t="n">
         <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
@@ -3950,91 +3950,91 @@
         <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Y14" t="n">
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
         <v>32</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO14" t="n">
         <v>55</v>
       </c>
-      <c r="AL14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>23</v>
-      </c>
       <c r="AP14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14" t="n">
         <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
         <v>11</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AX14" t="n">
         <v>18.5</v>
@@ -4046,22 +4046,22 @@
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
         <v>13.5</v>
@@ -4076,16 +4076,16 @@
         <v>10</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO14" t="n">
         <v>5.1</v>
@@ -4094,13 +4094,13 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14" t="n">
         <v>5.3</v>
@@ -4109,26 +4109,26 @@
         <v>3.9</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -4207,118 +4207,118 @@
         <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
         <v>2.44</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
+        <v>350</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>380</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK15" t="n">
         <v>65</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>970</v>
-      </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="AM15" t="n">
         <v>130</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO15" t="n">
         <v>120</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT15" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AU15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX15" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AY15" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BG15" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>3.95</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>3.8</v>
@@ -4443,7 +4443,7 @@
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
         <v>1.61</v>
@@ -4461,118 +4461,118 @@
         <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AA16" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
         <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH16" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AI16" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="AP16" t="n">
         <v>16</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV16" t="n">
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="n">
         <v>4.3</v>
@@ -4596,7 +4596,7 @@
         <v>5.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4667,25 +4667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G17" t="n">
         <v>1.32</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K17" t="n">
         <v>6.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -4694,10 +4694,10 @@
         <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
         <v>1.72</v>
@@ -4712,10 +4712,10 @@
         <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
         <v>4.1</v>
@@ -4724,10 +4724,10 @@
         <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z17" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4736,13 +4736,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE17" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AF17" t="n">
         <v>7.4</v>
@@ -4751,10 +4751,10 @@
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AJ17" t="n">
         <v>9.4</v>
@@ -4766,10 +4766,10 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -4778,13 +4778,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="AR17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS17" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>10</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4793,10 +4793,10 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX17" t="n">
         <v>6</v>
@@ -4805,10 +4805,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB17" t="n">
         <v>7.6</v>
@@ -4817,80 +4817,80 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI17" t="n">
         <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN17" t="n">
         <v>3.6</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BP17" t="n">
         <v>7.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR17" t="n">
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ17" t="n">
         <v>12</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
         <v>6.4</v>
@@ -4933,7 +4933,7 @@
         <v>7.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
@@ -4945,34 +4945,34 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
         <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
         <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X18" t="n">
         <v>11</v>
@@ -4981,52 +4981,52 @@
         <v>22</v>
       </c>
       <c r="Z18" t="n">
-        <v>70</v>
+        <v>350</v>
       </c>
       <c r="AA18" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>34</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AF18" t="n">
         <v>9.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>32</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ18" t="n">
         <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AN18" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AP18" t="n">
         <v>9</v>
@@ -5035,10 +5035,10 @@
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT18" t="n">
         <v>5.9</v>
@@ -5050,19 +5050,19 @@
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
         <v>6.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5071,16 +5071,16 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH18" t="n">
         <v>3</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H19" t="n">
         <v>15</v>
@@ -5187,25 +5187,25 @@
         <v>18.5</v>
       </c>
       <c r="J19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.31</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
         <v>1.92</v>
@@ -5214,7 +5214,7 @@
         <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
         <v>2.72</v>
@@ -5226,16 +5226,16 @@
         <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z19" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -5244,7 +5244,7 @@
         <v>7.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD19" t="n">
         <v>75</v>
@@ -5262,7 +5262,7 @@
         <v>55</v>
       </c>
       <c r="AI19" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AJ19" t="n">
         <v>9.199999999999999</v>
@@ -5274,7 +5274,7 @@
         <v>70</v>
       </c>
       <c r="AM19" t="n">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="AN19" t="n">
         <v>6.4</v>
@@ -5283,28 +5283,28 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
         <v>5.9</v>
       </c>
       <c r="AU19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV19" t="n">
         <v>42</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
         <v>5.8</v>
@@ -5313,28 +5313,28 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BA19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB19" t="n">
         <v>7.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
         <v>5.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH19" t="n">
         <v>3.75</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.42</v>
       </c>
       <c r="G20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H20" t="n">
         <v>10</v>
@@ -5441,10 +5441,10 @@
         <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -5462,7 +5462,7 @@
         <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
@@ -5489,7 +5489,7 @@
         <v>27</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -5501,22 +5501,22 @@
         <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE20" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AF20" t="n">
         <v>7.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>36</v>
       </c>
       <c r="AI20" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ20" t="n">
         <v>12</v>
@@ -5543,22 +5543,22 @@
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
         <v>5.7</v>
       </c>
       <c r="AU20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV20" t="n">
         <v>32</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>6.4</v>
@@ -5567,10 +5567,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB20" t="n">
         <v>9.199999999999999</v>
@@ -5579,16 +5579,16 @@
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
         <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="n">
         <v>3.3</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 16:54:20</t>
+          <t>2026-05-27 19:06:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
         <v>2.82</v>
@@ -869,7 +869,7 @@
         <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
@@ -884,13 +884,13 @@
         <v>2.96</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
@@ -917,10 +917,10 @@
         <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
         <v>9.800000000000001</v>
@@ -947,7 +947,7 @@
         <v>370</v>
       </c>
       <c r="AJ2" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
@@ -965,16 +965,16 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
         <v>7.6</v>
@@ -998,19 +998,19 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
@@ -1138,13 +1138,13 @@
         <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
         <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -1159,16 +1159,16 @@
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
         <v>100</v>
@@ -1186,7 +1186,7 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
         <v>25</v>
@@ -1198,25 +1198,25 @@
         <v>80</v>
       </c>
       <c r="AI3" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>95</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
         <v>8</v>
@@ -1228,7 +1228,7 @@
         <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1240,37 +1240,37 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX3" t="n">
         <v>9.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
         <v>6.2</v>
       </c>
       <c r="BE3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
         <v>3.15</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G4" t="n">
         <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I4" t="n">
         <v>2.36</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
         <v>1.43</v>
@@ -1467,10 +1467,10 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
         <v>7.8</v>
@@ -1491,13 +1491,13 @@
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1506,22 +1506,22 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
         <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
         <v>18</v>
@@ -1530,19 +1530,19 @@
         <v>3.05</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN4" t="n">
         <v>7.2</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT4" t="n">
         <v>5</v>
@@ -1572,13 +1572,13 @@
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1619,34 +1619,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P5" t="n">
         <v>1.61</v>
@@ -1655,25 +1655,25 @@
         <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
         <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1685,13 +1685,13 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1703,25 +1703,25 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AK5" t="n">
         <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1733,13 +1733,13 @@
         <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
@@ -1757,7 +1757,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1766,19 +1766,19 @@
         <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>3.15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H6" t="n">
         <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1897,7 +1897,7 @@
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O6" t="n">
         <v>1.59</v>
@@ -1921,7 +1921,7 @@
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
         <v>1.64</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>110</v>
@@ -1972,7 +1972,7 @@
         <v>160</v>
       </c>
       <c r="AM6" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN6" t="n">
         <v>40</v>
@@ -1987,25 +1987,25 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW6" t="n">
         <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
         <v>11</v>
@@ -2014,25 +2014,25 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="n">
         <v>2.64</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="n">
         <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K7" t="n">
         <v>3.05</v>
@@ -2151,28 +2151,28 @@
         <v>1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
         <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
         <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
         <v>1.47</v>
@@ -2211,43 +2211,43 @@
         <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="AJ7" t="n">
         <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
         <v>460</v>
       </c>
       <c r="AM7" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="AN7" t="n">
         <v>230</v>
       </c>
       <c r="AO7" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AP7" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
@@ -2256,49 +2256,49 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC7" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF7" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2319,38 +2319,38 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU7" t="n">
         <v>4.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
         <v>60</v>
       </c>
       <c r="BY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>9.4</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>70</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>9.6</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2381,67 +2381,67 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="K8" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
         <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
         <v>7.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
         <v>500</v>
@@ -2450,10 +2450,10 @@
         <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
         <v>290</v>
@@ -2465,25 +2465,25 @@
         <v>13.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK8" t="n">
-        <v>230</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
-        <v>460</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AO8" t="n">
         <v>390</v>
@@ -2492,10 +2492,10 @@
         <v>6.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
         <v>20</v>
@@ -2504,7 +2504,7 @@
         <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
@@ -2519,16 +2519,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD8" t="n">
         <v>9.6</v>
@@ -2561,40 +2561,40 @@
         <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ8" t="n">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
         <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>60</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
         <v>2.26</v>
@@ -2647,13 +2647,13 @@
         <v>2.46</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2686,7 +2686,7 @@
         <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
@@ -2752,7 +2752,7 @@
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2800,7 +2800,7 @@
         <v>3.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
         <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
         <v>1.94</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>2.96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I11" t="n">
         <v>3.1</v>
@@ -3161,7 +3161,7 @@
         <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -3212,7 +3212,7 @@
         <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>15</v>
@@ -3260,7 +3260,7 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -3284,19 +3284,19 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
         <v>6.2</v>
@@ -3308,7 +3308,7 @@
         <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="BJ11" t="n">
         <v>10</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.45</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.21</v>
@@ -3421,13 +3421,13 @@
         <v>1.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q12" t="n">
         <v>1.48</v>
@@ -3436,34 +3436,34 @@
         <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T12" t="n">
         <v>1.45</v>
       </c>
       <c r="U12" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
         <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Z12" t="n">
         <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AC12" t="n">
         <v>14.5</v>
@@ -3472,7 +3472,7 @@
         <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
         <v>90</v>
@@ -3487,25 +3487,25 @@
         <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AK12" t="n">
         <v>80</v>
       </c>
       <c r="AL12" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>220</v>
+        <v>970</v>
       </c>
       <c r="AO12" t="n">
         <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.4</v>
@@ -3514,13 +3514,13 @@
         <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AV12" t="n">
         <v>6.2</v>
@@ -3529,34 +3529,34 @@
         <v>9</v>
       </c>
       <c r="AX12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE12" t="n">
         <v>6.8</v>
       </c>
-      <c r="AY12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BF12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BH12" t="n">
         <v>4.9</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
         <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q13" t="n">
         <v>1.49</v>
@@ -3717,13 +3717,13 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
         <v>13</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE13" t="n">
         <v>32</v>
@@ -3762,10 +3762,10 @@
         <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AS13" t="n">
         <v>4.3</v>
@@ -3780,10 +3780,10 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
         <v>9.199999999999999</v>
@@ -3798,10 +3798,10 @@
         <v>16</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BE13" t="n">
         <v>4.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -3905,28 +3905,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
         <v>3.75</v>
@@ -3935,7 +3935,7 @@
         <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
         <v>1.96</v>
@@ -3947,7 +3947,7 @@
         <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
         <v>2.18</v>
@@ -3965,7 +3965,7 @@
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
         <v>90</v>
@@ -4049,16 +4049,16 @@
         <v>20</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC14" t="n">
         <v>7.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>1.69</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I15" t="n">
         <v>7.4</v>
@@ -4207,7 +4207,7 @@
         <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
         <v>2.44</v>
@@ -4216,7 +4216,7 @@
         <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
         <v>350</v>
@@ -4231,7 +4231,7 @@
         <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
         <v>400</v>
@@ -4243,7 +4243,7 @@
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
         <v>380</v>
@@ -4270,7 +4270,7 @@
         <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR15" t="n">
         <v>7</v>
@@ -4288,7 +4288,7 @@
         <v>6</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
         <v>5.1</v>
@@ -4300,22 +4300,22 @@
         <v>5.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB15" t="n">
         <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD15" t="n">
         <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
         <v>7.4</v>
@@ -4324,65 +4324,65 @@
         <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BN15" t="n">
         <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
         <v>3.95</v>
@@ -4425,10 +4425,10 @@
         <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.26</v>
@@ -4464,7 +4464,7 @@
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
         <v>90</v>
@@ -4479,7 +4479,7 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -4542,7 +4542,7 @@
         <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -4614,7 +4614,7 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>1.27</v>
       </c>
       <c r="G17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
         <v>5.7</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -4700,34 +4700,34 @@
         <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V17" t="n">
         <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Z17" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -4742,22 +4742,22 @@
         <v>60</v>
       </c>
       <c r="AE17" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="AF17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI17" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK17" t="n">
         <v>16.5</v>
@@ -4766,10 +4766,10 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -4778,13 +4778,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>6.8</v>
@@ -4793,22 +4793,22 @@
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="AW17" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>32</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>7.6</v>
@@ -4817,16 +4817,16 @@
         <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH17" t="n">
         <v>4.1</v>
@@ -4838,13 +4838,13 @@
         <v>15</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN17" t="n">
         <v>3.6</v>
@@ -4856,16 +4856,16 @@
         <v>7.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
         <v>29</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU17" t="n">
         <v>7.2</v>
@@ -4874,7 +4874,7 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>12</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -4921,31 +4921,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>1.41</v>
@@ -4957,7 +4957,7 @@
         <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
         <v>4.2</v>
@@ -4966,13 +4966,13 @@
         <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
         <v>1.15</v>
       </c>
       <c r="W18" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X18" t="n">
         <v>11</v>
@@ -4984,13 +4984,13 @@
         <v>350</v>
       </c>
       <c r="AA18" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
         <v>34</v>
@@ -4999,10 +4999,10 @@
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
         <v>32</v>
@@ -5029,40 +5029,40 @@
         <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS18" t="n">
         <v>6.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
         <v>6.8</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5071,19 +5071,19 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BI18" t="n">
         <v>2.42</v>
@@ -5092,13 +5092,13 @@
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN18" t="n">
         <v>4.2</v>
@@ -5110,41 +5110,41 @@
         <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT18" t="n">
         <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ18" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H19" t="n">
         <v>15</v>
@@ -5187,46 +5187,46 @@
         <v>18.5</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="K19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.31</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V19" t="n">
         <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X19" t="n">
         <v>18.5</v>
@@ -5241,34 +5241,34 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="AF19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG19" t="n">
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI19" t="n">
         <v>370</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>70</v>
@@ -5277,64 +5277,64 @@
         <v>490</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AP19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX19" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>36</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB19" t="n">
         <v>7.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="n">
         <v>3.75</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="G20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -5456,7 +5456,7 @@
         <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
         <v>1.77</v>
@@ -5471,25 +5471,25 @@
         <v>3.95</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V20" t="n">
         <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z20" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -5504,22 +5504,22 @@
         <v>42</v>
       </c>
       <c r="AE20" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AF20" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI20" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK20" t="n">
         <v>20</v>
@@ -5528,10 +5528,10 @@
         <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -5540,25 +5540,25 @@
         <v>9.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>5.7</v>
       </c>
       <c r="AU20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW20" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>6.4</v>
@@ -5567,10 +5567,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BB20" t="n">
         <v>9.199999999999999</v>
@@ -5579,22 +5579,22 @@
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG20" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>10</v>
       </c>
       <c r="BH20" t="n">
         <v>3.3</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ20" t="n">
         <v>14</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 19:06:11</t>
+          <t>2026-05-27 21:18:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
         <v>3.4</v>
@@ -875,13 +875,13 @@
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.4</v>
@@ -890,49 +890,49 @@
         <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AF2" t="n">
         <v>17.5</v>
@@ -941,52 +941,52 @@
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="AJ2" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP2" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AX2" t="n">
         <v>13.5</v>
@@ -995,82 +995,82 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN2" t="n">
         <v>5.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP2" t="n">
         <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1114,61 +1114,61 @@
         <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>100</v>
@@ -1189,7 +1189,7 @@
         <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
         <v>30</v>
@@ -1213,34 +1213,34 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX3" t="n">
         <v>9.6</v>
@@ -1249,49 +1249,49 @@
         <v>7.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.73</v>
+        <v>7.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO3" t="n">
         <v>3.6</v>
@@ -1300,25 +1300,25 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>6.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1365,61 +1365,61 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
         <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="V4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
         <v>9.6</v>
@@ -1431,7 +1431,7 @@
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
         <v>9</v>
@@ -1458,7 +1458,7 @@
         <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AL4" t="n">
         <v>200</v>
@@ -1467,118 +1467,118 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
         <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF4" t="n">
         <v>12</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
         <v>7.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
         <v>5</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
         <v>18.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.46</v>
@@ -1655,28 +1655,28 @@
         <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
         <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
         <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
         <v>400</v>
@@ -1703,7 +1703,7 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1727,22 +1727,22 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
         <v>14.5</v>
@@ -1754,10 +1754,10 @@
         <v>6.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
@@ -1766,13 +1766,13 @@
         <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
         <v>8.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
@@ -1781,68 +1781,68 @@
         <v>4.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>8</v>
       </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -1882,31 +1882,31 @@
         <v>3.85</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
         <v>1.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,19 +1915,19 @@
         <v>6.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
         <v>1.64</v>
       </c>
       <c r="X6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
         <v>12</v>
@@ -1936,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
         <v>7.6</v>
@@ -1948,7 +1948,7 @@
         <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1957,7 +1957,7 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
         <v>110</v>
@@ -1969,31 +1969,31 @@
         <v>80</v>
       </c>
       <c r="AL6" t="n">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AM6" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AO6" t="n">
         <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS6" t="n">
         <v>10.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
@@ -2002,7 +2002,7 @@
         <v>15.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -2011,34 +2011,34 @@
         <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BD6" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BE6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG6" t="n">
         <v>11</v>
       </c>
-      <c r="BF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH6" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
@@ -2056,7 +2056,7 @@
         <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP6" t="n">
         <v>21</v>
@@ -2065,10 +2065,10 @@
         <v>9.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
@@ -2077,26 +2077,26 @@
         <v>5.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
         <v>14</v>
       </c>
       <c r="BZ6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>3.05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="M7" t="n">
         <v>1.15</v>
@@ -2172,7 +2172,7 @@
         <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
         <v>1.47</v>
@@ -2187,7 +2187,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
         <v>130</v>
@@ -2199,13 +2199,13 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG7" t="n">
         <v>15.5</v>
@@ -2229,10 +2229,10 @@
         <v>230</v>
       </c>
       <c r="AN7" t="n">
-        <v>230</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
         <v>6.4</v>
@@ -2241,52 +2241,52 @@
         <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
         <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>2.62</v>
@@ -2319,7 +2319,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
         <v>9.199999999999999</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2384,19 +2384,19 @@
         <v>2.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I8" t="n">
         <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L8" t="n">
         <v>1.63</v>
@@ -2405,16 +2405,16 @@
         <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O8" t="n">
         <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
@@ -2426,13 +2426,13 @@
         <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V8" t="n">
         <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
         <v>7.6</v>
@@ -2453,7 +2453,7 @@
         <v>6.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>290</v>
@@ -2471,7 +2471,7 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AK8" t="n">
         <v>42</v>
@@ -2483,10 +2483,10 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>6.4</v>
@@ -2498,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2510,28 +2510,28 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE8" t="n">
         <v>10.5</v>
@@ -2540,7 +2540,7 @@
         <v>32</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BH8" t="n">
         <v>2.66</v>
@@ -2564,7 +2564,7 @@
         <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
         <v>25</v>
@@ -2582,7 +2582,7 @@
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
         <v>38</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
         <v>2.26</v>
       </c>
       <c r="I9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J9" t="n">
         <v>3.35</v>
@@ -2653,40 +2653,40 @@
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.34</v>
       </c>
-      <c r="P9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
         <v>16</v>
@@ -2695,7 +2695,7 @@
         <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
         <v>34</v>
@@ -2710,10 +2710,10 @@
         <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>17</v>
@@ -2722,46 +2722,46 @@
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
         <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
         <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
         <v>19.5</v>
@@ -2773,92 +2773,92 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG9" t="n">
         <v>16</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BN9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS9" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>8</v>
       </c>
       <c r="BT9" t="n">
         <v>5.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BV9" t="n">
         <v>18</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G10" t="n">
         <v>2.06</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
         <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
@@ -2919,7 +2919,7 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
         <v>2.16</v>
@@ -2937,16 +2937,16 @@
         <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
         <v>1.94</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
         <v>38</v>
@@ -2976,10 +2976,10 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
         <v>25</v>
@@ -2991,7 +2991,7 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>290</v>
@@ -3003,10 +3003,10 @@
         <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>6.2</v>
@@ -3018,37 +3018,37 @@
         <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
         <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
         <v>17.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC10" t="n">
         <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.2</v>
@@ -3060,13 +3060,13 @@
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>4.7</v>
@@ -3078,16 +3078,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR10" t="n">
         <v>36</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU10" t="n">
         <v>4.4</v>
@@ -3096,23 +3096,23 @@
         <v>48</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>65</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>34</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3146,58 +3146,58 @@
         <v>2.62</v>
       </c>
       <c r="G11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
         <v>11.5</v>
@@ -3215,16 +3215,16 @@
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF11" t="n">
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -3233,22 +3233,22 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>440</v>
       </c>
       <c r="AN11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO11" t="n">
         <v>32</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>36</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -3260,13 +3260,13 @@
         <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
         <v>9.800000000000001</v>
@@ -3284,67 +3284,67 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO11" t="n">
         <v>4.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11" t="n">
         <v>6.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
         <v>24</v>
@@ -3353,20 +3353,20 @@
         <v>7.4</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3397,28 +3397,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.21</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
         <v>6.2</v>
@@ -3427,10 +3427,10 @@
         <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="R12" t="n">
         <v>1.7</v>
@@ -3439,40 +3439,40 @@
         <v>2.14</v>
       </c>
       <c r="T12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U12" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
         <v>970</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD12" t="n">
         <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AF12" t="n">
         <v>90</v>
@@ -3481,7 +3481,7 @@
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>48</v>
@@ -3505,7 +3505,7 @@
         <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>8.4</v>
@@ -3514,13 +3514,13 @@
         <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AV12" t="n">
         <v>6.2</v>
@@ -3529,34 +3529,34 @@
         <v>9</v>
       </c>
       <c r="AX12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH12" t="n">
         <v>4.9</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
         <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -3702,7 +3702,7 @@
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X13" t="n">
         <v>36</v>
@@ -3777,7 +3777,7 @@
         <v>7.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
         <v>13</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -3905,34 +3905,34 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
         <v>3.65</v>
       </c>
       <c r="H14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I14" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
         <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
         <v>1.89</v>
@@ -3950,16 +3950,16 @@
         <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
         <v>12</v>
@@ -3971,19 +3971,19 @@
         <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>65</v>
       </c>
       <c r="AF14" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AG14" t="n">
         <v>21</v>
@@ -4010,13 +4010,13 @@
         <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AP14" t="n">
         <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
         <v>10.5</v>
@@ -4049,7 +4049,7 @@
         <v>20</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
         <v>7.8</v>
@@ -4058,7 +4058,7 @@
         <v>7.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H15" t="n">
         <v>5.3</v>
@@ -4207,10 +4207,10 @@
         <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4455,10 +4455,10 @@
         <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
@@ -4491,7 +4491,7 @@
         <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
         <v>36</v>
@@ -4578,7 +4578,7 @@
         <v>4.3</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>1.27</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
         <v>5.7</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -4700,7 +4700,7 @@
         <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
         <v>1.43</v>
@@ -4712,7 +4712,7 @@
         <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
         <v>1.06</v>
@@ -4721,43 +4721,43 @@
         <v>4.2</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Z17" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AB17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD17" t="n">
         <v>60</v>
       </c>
       <c r="AE17" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AF17" t="n">
         <v>7.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
         <v>42</v>
       </c>
       <c r="AI17" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AK17" t="n">
         <v>16.5</v>
@@ -4766,67 +4766,67 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AP17" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AQ17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT17" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
         <v>6.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD17" t="n">
         <v>42</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BH17" t="n">
         <v>4.1</v>
@@ -4844,7 +4844,7 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN17" t="n">
         <v>3.6</v>
@@ -4856,10 +4856,10 @@
         <v>7.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS17" t="n">
         <v>8.6</v>
@@ -4880,7 +4880,7 @@
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>12</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="G18" t="n">
         <v>1.69</v>
@@ -4930,7 +4930,7 @@
         <v>6.6</v>
       </c>
       <c r="I18" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.85</v>
@@ -4942,10 +4942,10 @@
         <v>1.53</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>1.41</v>
@@ -4963,13 +4963,13 @@
         <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
         <v>2.44</v>
@@ -4978,7 +4978,7 @@
         <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="n">
         <v>350</v>
@@ -4990,7 +4990,7 @@
         <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>34</v>
@@ -4999,7 +4999,7 @@
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
@@ -5050,7 +5050,7 @@
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
         <v>6.8</v>
@@ -5062,7 +5062,7 @@
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G19" t="n">
         <v>1.31</v>
       </c>
       <c r="H19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
         <v>18.5</v>
       </c>
       <c r="J19" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K19" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -5214,13 +5214,13 @@
         <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
         <v>2.68</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
         <v>1.05</v>
@@ -5229,19 +5229,19 @@
         <v>4.2</v>
       </c>
       <c r="X19" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
         <v>40</v>
       </c>
       <c r="Z19" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC19" t="n">
         <v>15.5</v>
@@ -5250,16 +5250,16 @@
         <v>70</v>
       </c>
       <c r="AE19" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AF19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AG19" t="n">
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI19" t="n">
         <v>370</v>
@@ -5289,34 +5289,34 @@
         <v>32</v>
       </c>
       <c r="AR19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS19" t="n">
         <v>9</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.4</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AW19" t="n">
         <v>9</v>
       </c>
-      <c r="AW19" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AX19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB19" t="n">
         <v>7.8</v>
@@ -5325,16 +5325,16 @@
         <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
         <v>5</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="n">
         <v>3.75</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
         <v>1.48</v>
       </c>
       <c r="H20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>11.5</v>
@@ -5453,13 +5453,13 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
         <v>2.12</v>
@@ -5468,25 +5468,25 @@
         <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
         <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z20" t="n">
         <v>95</v>
@@ -5498,7 +5498,7 @@
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
         <v>42</v>
@@ -5507,70 +5507,70 @@
         <v>250</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AI20" t="n">
         <v>210</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
         <v>310</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="AP20" t="n">
         <v>9.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU20" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>9</v>
-      </c>
       <c r="AV20" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>7.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB20" t="n">
         <v>9.199999999999999</v>
@@ -5579,22 +5579,22 @@
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="n">
         <v>3.3</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ20" t="n">
         <v>14</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN20" t="n">
         <v>3.6</v>
@@ -5618,10 +5618,10 @@
         <v>9</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
         <v>10</v>
@@ -5636,23 +5636,23 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>20</v>
       </c>
       <c r="CA20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 21:18:31</t>
+          <t>2026-05-27 23:30:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -860,181 +860,181 @@
         <v>2.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
         <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>130</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>100</v>
-      </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>16</v>
       </c>
-      <c r="AT2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="BD2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>11</v>
-      </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>5.9</v>
@@ -1043,34 +1043,34 @@
         <v>4.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT2" t="n">
+      <c r="BU2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -1111,61 +1111,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
         <v>4.9</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
@@ -1177,34 +1177,34 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL3" t="n">
         <v>500</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
@@ -1222,28 +1222,28 @@
         <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
         <v>7.6</v>
@@ -1252,64 +1252,64 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>4</v>
       </c>
       <c r="BH3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK3" t="n">
         <v>3.25</v>
       </c>
-      <c r="BI3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="BN3" t="n">
         <v>4.9</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
         <v>5.6</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -1365,76 +1365,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
         <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P4" t="n">
         <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V4" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>9.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA4" t="n">
         <v>38</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>14</v>
@@ -1452,16 +1452,16 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AJ4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
         <v>370</v>
       </c>
       <c r="AL4" t="n">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1473,112 +1473,112 @@
         <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>22</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>22</v>
+        <v>5.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>23</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>12</v>
       </c>
       <c r="BG4" t="n">
         <v>5.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>2.36</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>2.28</v>
       </c>
       <c r="BT4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.6</v>
+        <v>2.26</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
@@ -1631,97 +1631,97 @@
         <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
         <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>400</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB5" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1730,64 +1730,64 @@
         <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BK5" t="n">
         <v>6.4</v>
@@ -1796,16 +1796,16 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.199999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO5" t="n">
         <v>3.35</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ5" t="n">
         <v>5.9</v>
@@ -1814,10 +1814,10 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU5" t="n">
         <v>6</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -1876,43 +1876,43 @@
         <v>2.42</v>
       </c>
       <c r="G6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.51</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.53</v>
-      </c>
       <c r="Q6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="T6" t="n">
         <v>2.14</v>
@@ -1921,16 +1921,16 @@
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
         <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
         <v>26</v>
@@ -1945,10 +1945,10 @@
         <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>70</v>
+        <v>440</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1957,10 +1957,10 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AJ6" t="n">
         <v>38</v>
@@ -1969,10 +1969,10 @@
         <v>80</v>
       </c>
       <c r="AL6" t="n">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
         <v>110</v>
@@ -1984,25 +1984,25 @@
         <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -2011,92 +2011,92 @@
         <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BB6" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC6" t="n">
         <v>30</v>
       </c>
       <c r="BD6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="n">
         <v>2.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
         <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
         <v>38</v>
       </c>
       <c r="BW6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
         <v>12</v>
       </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>14</v>
-      </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -2133,49 +2133,49 @@
         <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
         <v>1.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
         <v>1.45</v>
@@ -2196,19 +2196,19 @@
         <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
         <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -2226,7 +2226,7 @@
         <v>460</v>
       </c>
       <c r="AM7" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN7" t="n">
         <v>600</v>
@@ -2238,73 +2238,73 @@
         <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
         <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,13 +2316,13 @@
         <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>5.9</v>
@@ -2334,23 +2334,23 @@
         <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX7" t="n">
         <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -2381,40 +2381,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K8" t="n">
         <v>2.88</v>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
         <v>1.17</v>
@@ -2423,46 +2423,46 @@
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>7.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>290</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
@@ -2474,7 +2474,7 @@
         <v>120</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
         <v>160</v>
@@ -2483,19 +2483,19 @@
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
         <v>30</v>
@@ -2504,13 +2504,13 @@
         <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
@@ -2519,40 +2519,40 @@
         <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>18</v>
       </c>
-      <c r="BC8" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE8" t="n">
         <v>10</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
         <v>32</v>
       </c>
       <c r="BG8" t="n">
-        <v>17.5</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,50 +2561,50 @@
         <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>60</v>
       </c>
       <c r="CA8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -2638,61 +2638,61 @@
         <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
         <v>18</v>
@@ -2704,7 +2704,7 @@
         <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
         <v>14</v>
@@ -2713,7 +2713,7 @@
         <v>27</v>
       </c>
       <c r="AF9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG9" t="n">
         <v>17</v>
@@ -2725,13 +2725,13 @@
         <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AK9" t="n">
         <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
@@ -2743,58 +2743,58 @@
         <v>21</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>3.85</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>19.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>16.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>16</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="n">
         <v>3.45</v>
@@ -2803,7 +2803,7 @@
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK9" t="n">
         <v>5.5</v>
@@ -2812,10 +2812,10 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>2.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO9" t="n">
         <v>5.7</v>
@@ -2827,7 +2827,7 @@
         <v>8.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS9" t="n">
         <v>9.199999999999999</v>
@@ -2836,10 +2836,10 @@
         <v>5.3</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW9" t="n">
         <v>7</v>
@@ -2854,11 +2854,11 @@
         <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -2889,175 +2889,175 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>19</v>
       </c>
-      <c r="AO10" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK10" t="n">
         <v>5.1</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
         <v>8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -3143,64 +3143,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
         <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
         <v>22</v>
@@ -3212,10 +3212,10 @@
         <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>34</v>
@@ -3242,85 +3242,85 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO11" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
         <v>5.9</v>
@@ -3338,13 +3338,13 @@
         <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT11" t="n">
         <v>6.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV11" t="n">
         <v>24</v>
@@ -3356,17 +3356,17 @@
         <v>38</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>32</v>
       </c>
       <c r="CA11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -3397,70 +3397,70 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="T12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
         <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
@@ -3469,22 +3469,22 @@
         <v>17.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
         <v>90</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AH12" t="n">
         <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
         <v>500</v>
@@ -3502,61 +3502,61 @@
         <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT12" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC12" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX12" t="n">
+      <c r="BD12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF12" t="n">
         <v>8</v>
       </c>
-      <c r="AY12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC12" t="n">
+      <c r="BG12" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.6</v>
       </c>
       <c r="BH12" t="n">
         <v>4.9</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
         <v>7.6</v>
@@ -3592,7 +3592,7 @@
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT12" t="n">
         <v>5.7</v>
@@ -3601,7 +3601,7 @@
         <v>4.2</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW12" t="n">
         <v>6</v>
@@ -3610,17 +3610,17 @@
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA12" t="n">
         <v>6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -3651,61 +3651,61 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I13" t="n">
         <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T13" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="U13" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y13" t="n">
         <v>24</v>
@@ -3723,7 +3723,7 @@
         <v>13</v>
       </c>
       <c r="AD13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>32</v>
@@ -3732,7 +3732,7 @@
         <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
         <v>17.5</v>
@@ -3741,10 +3741,10 @@
         <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>34</v>
@@ -3753,10 +3753,10 @@
         <v>60</v>
       </c>
       <c r="AN13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
         <v>14.5</v>
@@ -3768,113 +3768,113 @@
         <v>21</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD13" t="n">
         <v>21</v>
       </c>
-      <c r="BB13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>13</v>
-      </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BJ13" t="n">
         <v>8.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN13" t="n">
         <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW13" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>8</v>
-      </c>
       <c r="BX13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BY13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CA13" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G14" t="n">
         <v>3.65</v>
@@ -3920,10 +3920,10 @@
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3932,22 +3932,22 @@
         <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
         <v>2.14</v>
@@ -3959,25 +3959,25 @@
         <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
         <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
         <v>65</v>
@@ -3989,16 +3989,16 @@
         <v>21</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AI14" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -4007,64 +4007,64 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AP14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR14" t="n">
         <v>12</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
         <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
         <v>11.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.45</v>
@@ -4076,59 +4076,59 @@
         <v>10</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
         <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV14" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
         <v>7.8</v>
       </c>
-      <c r="BZ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>7.6</v>
-      </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -4162,73 +4162,73 @@
         <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
         <v>4</v>
       </c>
-      <c r="K15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.65</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
         <v>350</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -4237,10 +4237,10 @@
         <v>400</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -4249,140 +4249,140 @@
         <v>380</v>
       </c>
       <c r="AJ15" t="n">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AL15" t="n">
         <v>150</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AO15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AV15" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY15" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB15" t="n">
         <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BG15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>970</v>
+      </c>
+      <c r="CA15" t="n">
         <v>7.4</v>
       </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -4416,55 +4416,55 @@
         <v>1.85</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="H16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.61</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.52</v>
-      </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T16" t="n">
         <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="X16" t="n">
         <v>90</v>
@@ -4479,7 +4479,7 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
@@ -4491,7 +4491,7 @@
         <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AG16" t="n">
         <v>36</v>
@@ -4515,22 +4515,22 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
         <v>250</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR16" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR16" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AS16" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -4539,10 +4539,10 @@
         <v>5.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -4551,31 +4551,31 @@
         <v>5.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD16" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI16" t="n">
         <v>3.6</v>
@@ -4584,13 +4584,13 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN16" t="n">
         <v>5.1</v>
@@ -4602,41 +4602,41 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -4670,181 +4670,181 @@
         <v>1.27</v>
       </c>
       <c r="G17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="H17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I17" t="n">
         <v>14.5</v>
       </c>
-      <c r="I17" t="n">
-        <v>18</v>
-      </c>
       <c r="J17" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>800</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>300</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL17" t="n">
         <v>44</v>
       </c>
-      <c r="Z17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>960</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>360</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
       <c r="AM17" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>570</v>
+        <v>390</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV17" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AW17" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>12</v>
       </c>
       <c r="BN17" t="n">
         <v>3.6</v>
@@ -4853,16 +4853,16 @@
         <v>3.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
         <v>17.5</v>
@@ -4874,23 +4874,23 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ17" t="n">
         <v>11.5</v>
       </c>
-      <c r="BX17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>12</v>
-      </c>
       <c r="CA17" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
         <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.53</v>
@@ -4945,28 +4945,28 @@
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.18</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.16</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
@@ -4978,7 +4978,7 @@
         <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
         <v>350</v>
@@ -4987,22 +4987,22 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
         <v>32</v>
@@ -5011,19 +5011,19 @@
         <v>700</v>
       </c>
       <c r="AJ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK18" t="n">
         <v>21</v>
       </c>
-      <c r="AK18" t="n">
-        <v>65</v>
-      </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="AM18" t="n">
         <v>700</v>
       </c>
       <c r="AN18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
@@ -5032,13 +5032,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
         <v>5.8</v>
@@ -5050,19 +5050,19 @@
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5071,80 +5071,80 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO18" t="n">
         <v>3.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BT18" t="n">
         <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -5175,67 +5175,67 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I19" t="n">
         <v>18.5</v>
       </c>
       <c r="J19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
         <v>1.31</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
         <v>40</v>
       </c>
       <c r="Z19" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
@@ -5244,118 +5244,118 @@
         <v>7.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD19" t="n">
         <v>70</v>
       </c>
       <c r="AE19" t="n">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="AF19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI19" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM19" t="n">
-        <v>490</v>
+        <v>400</v>
       </c>
       <c r="AN19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>880</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT19" t="n">
         <v>6.2</v>
       </c>
-      <c r="AO19" t="n">
-        <v>990</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6</v>
-      </c>
       <c r="AU19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AW19" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
         <v>6</v>
       </c>
       <c r="AY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>9</v>
-      </c>
       <c r="BH19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BO19" t="n">
         <v>2.68</v>
@@ -5370,35 +5370,35 @@
         <v>34</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ19" t="n">
         <v>14.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>
@@ -5429,205 +5429,205 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H20" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I20" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
         <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z20" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB20" t="n">
         <v>6.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE20" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AF20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AI20" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
         <v>310</v>
       </c>
       <c r="AN20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
-        <v>510</v>
+        <v>400</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>5.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
         <v>44</v>
       </c>
       <c r="BE20" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI20" t="n">
         <v>2.72</v>
       </c>
       <c r="BJ20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN20" t="n">
         <v>3.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BP20" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BU20" t="n">
         <v>7.2</v>
@@ -5636,23 +5636,23 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-27 23:30:07</t>
+          <t>2026-05-28 01:43:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,91 +857,91 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.96</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
         <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>370</v>
@@ -953,124 +953,124 @@
         <v>80</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11</v>
       </c>
       <c r="AW2" t="n">
         <v>18</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BD2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK2" t="n">
         <v>8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
         <v>100</v>
@@ -1177,31 +1177,31 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
         <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AF3" t="n">
         <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
         <v>60</v>
       </c>
       <c r="AI3" t="n">
+        <v>450</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>500</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>110</v>
       </c>
       <c r="AK3" t="n">
         <v>100</v>
@@ -1213,7 +1213,7 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
@@ -1222,25 +1222,25 @@
         <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1252,46 +1252,46 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
         <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO3" t="n">
         <v>3.65</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1365,40 +1365,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
         <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
         <v>1.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.21</v>
@@ -1407,55 +1407,55 @@
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W4" t="n">
         <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AI4" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AK4" t="n">
         <v>370</v>
@@ -1470,79 +1470,79 @@
         <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AV4" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.36</v>
+        <v>15</v>
       </c>
       <c r="BN4" t="n">
         <v>6.8</v>
@@ -1554,31 +1554,31 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.28</v>
+        <v>12.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
         <v>4.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.26</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1622,55 +1622,55 @@
         <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
         <v>4.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
@@ -1682,22 +1682,22 @@
         <v>65</v>
       </c>
       <c r="AA5" t="n">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG5" t="n">
         <v>9.4</v>
@@ -1706,67 +1706,67 @@
         <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AJ5" t="n">
         <v>16</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>46</v>
+        <v>19.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS5" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
         <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
         <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
         <v>27</v>
@@ -1775,10 +1775,10 @@
         <v>17.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.1</v>
@@ -1790,59 +1790,59 @@
         <v>95</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP5" t="n">
         <v>11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>11.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>2.46</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
@@ -1885,218 +1885,218 @@
         <v>3.95</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
         <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X6" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="Y6" t="n">
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>440</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL6" t="n">
         <v>460</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>70</v>
-      </c>
       <c r="AM6" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
         <v>110</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD6" t="n">
         <v>27</v>
       </c>
-      <c r="AX6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>28</v>
-      </c>
       <c r="BE6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BT6" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.8</v>
       </c>
       <c r="BU6" t="n">
         <v>5.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BZ6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="CA6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2127,88 +2127,88 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q7" t="n">
         <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
         <v>6.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG7" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -2217,79 +2217,79 @@
         <v>200</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="AM7" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AN7" t="n">
-        <v>600</v>
+        <v>230</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR7" t="n">
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>7.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BI7" t="n">
         <v>2.18</v>
@@ -2298,59 +2298,59 @@
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
         <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2381,85 +2381,85 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M8" t="n">
         <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AG8" t="n">
         <v>14</v>
@@ -2468,31 +2468,31 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL8" t="n">
         <v>120</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>160</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
@@ -2501,10 +2501,10 @@
         <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
@@ -2513,7 +2513,7 @@
         <v>21</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
@@ -2522,31 +2522,31 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
         <v>18.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BF8" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ8" t="n">
         <v>12</v>
@@ -2561,16 +2561,16 @@
         <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
         <v>55</v>
@@ -2579,19 +2579,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
@@ -2659,55 +2659,55 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
         <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
         <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>27</v>
@@ -2716,10 +2716,10 @@
         <v>26</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
         <v>42</v>
@@ -2731,109 +2731,109 @@
         <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO9" t="n">
         <v>21</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>2.62</v>
+        <v>14</v>
       </c>
       <c r="BN9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BR9" t="n">
         <v>40</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU9" t="n">
         <v>4.6</v>
@@ -2842,23 +2842,23 @@
         <v>17.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9" t="n">
         <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="H10" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="X10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN10" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>130</v>
       </c>
       <c r="AP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS10" t="n">
         <v>11</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="AT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8</v>
-      </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BG10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BN10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA10" t="n">
         <v>7.8</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>27</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H11" t="n">
         <v>2.72</v>
@@ -3158,7 +3158,7 @@
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.44</v>
@@ -3170,10 +3170,10 @@
         <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
         <v>2.08</v>
@@ -3182,10 +3182,10 @@
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
         <v>2.06</v>
@@ -3194,10 +3194,10 @@
         <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
@@ -3209,16 +3209,16 @@
         <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AF11" t="n">
         <v>21</v>
@@ -3245,85 +3245,85 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
         <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
         <v>16.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY11" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
         <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO11" t="n">
         <v>4.5</v>
@@ -3332,41 +3332,41 @@
         <v>22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11" t="n">
         <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU11" t="n">
         <v>4.6</v>
       </c>
       <c r="BV11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BX11" t="n">
         <v>38</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>32</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3397,58 +3397,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="S12" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="T12" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="V12" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>90</v>
@@ -3466,10 +3466,10 @@
         <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
         <v>34</v>
@@ -3484,7 +3484,7 @@
         <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
         <v>500</v>
@@ -3502,125 +3502,125 @@
         <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD12" t="n">
         <v>13.5</v>
       </c>
-      <c r="BB12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BE12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BF12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH12" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA12" t="n">
         <v>7.4</v>
       </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>6</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.24</v>
@@ -3675,10 +3675,10 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
         <v>3.15</v>
@@ -3702,13 +3702,13 @@
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
         <v>38</v>
       </c>
       <c r="Y13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="n">
         <v>30</v>
@@ -3717,10 +3717,10 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AD13" t="n">
         <v>16</v>
@@ -3741,7 +3741,7 @@
         <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AK13" t="n">
         <v>25</v>
@@ -3750,34 +3750,34 @@
         <v>34</v>
       </c>
       <c r="AM13" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
         <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
         <v>22</v>
@@ -3801,22 +3801,22 @@
         <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>18.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ13" t="n">
         <v>8.4</v>
@@ -3831,13 +3831,13 @@
         <v>12</v>
       </c>
       <c r="BN13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ13" t="n">
         <v>7.4</v>
@@ -3852,7 +3852,7 @@
         <v>7</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV13" t="n">
         <v>18.5</v>
@@ -3861,20 +3861,20 @@
         <v>8.4</v>
       </c>
       <c r="BX13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3911,19 +3911,19 @@
         <v>3.65</v>
       </c>
       <c r="H14" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3935,7 +3935,7 @@
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
         <v>2.02</v>
@@ -3944,16 +3944,16 @@
         <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W14" t="n">
         <v>1.38</v>
@@ -3962,19 +3962,19 @@
         <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
         <v>15</v>
       </c>
       <c r="AA14" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
         <v>11.5</v>
@@ -3983,7 +3983,7 @@
         <v>65</v>
       </c>
       <c r="AF14" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
         <v>21</v>
@@ -3995,10 +3995,10 @@
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -4010,7 +4010,7 @@
         <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP14" t="n">
         <v>12.5</v>
@@ -4022,79 +4022,79 @@
         <v>12</v>
       </c>
       <c r="AS14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AX14" t="n">
         <v>20</v>
       </c>
       <c r="AY14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.45</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ14" t="n">
         <v>10</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO14" t="n">
         <v>5</v>
       </c>
       <c r="BP14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4103,32 +4103,32 @@
         <v>8.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU14" t="n">
         <v>3.95</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW14" t="n">
         <v>6.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA14" t="n">
         <v>7.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4159,85 +4159,85 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
         <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V15" t="n">
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="X15" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="Z15" t="n">
-        <v>350</v>
+        <v>160</v>
       </c>
       <c r="AA15" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
@@ -4246,7 +4246,7 @@
         <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>380</v>
+        <v>240</v>
       </c>
       <c r="AJ15" t="n">
         <v>22</v>
@@ -4258,25 +4258,25 @@
         <v>150</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO15" t="n">
         <v>140</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -4285,67 +4285,67 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7</v>
       </c>
       <c r="BC15" t="n">
         <v>9</v>
       </c>
       <c r="BD15" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15" t="n">
         <v>11</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>5.6</v>
@@ -4354,35 +4354,35 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4413,52 +4413,52 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
         <v>4.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
@@ -4491,7 +4491,7 @@
         <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
         <v>36</v>
@@ -4515,22 +4515,22 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR16" t="n">
         <v>14.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -4539,10 +4539,10 @@
         <v>5.6</v>
       </c>
       <c r="AV16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW16" t="n">
         <v>9</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>8.4</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -4551,92 +4551,92 @@
         <v>5.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
         <v>8.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>6.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.27</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="H17" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="J17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K17" t="n">
         <v>7.2</v>
@@ -4697,67 +4697,67 @@
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
         <v>1.53</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Y17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z17" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA17" t="n">
         <v>800</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AD17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE17" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AI17" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>9.4</v>
       </c>
       <c r="AK17" t="n">
         <v>15.5</v>
@@ -4766,22 +4766,22 @@
         <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="AP17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS17" t="n">
         <v>13</v>
@@ -4790,46 +4790,46 @@
         <v>7.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW17" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
       </c>
       <c r="BD17" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF17" t="n">
         <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI17" t="n">
         <v>3.45</v>
@@ -4838,13 +4838,13 @@
         <v>14.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN17" t="n">
         <v>3.6</v>
@@ -4856,41 +4856,41 @@
         <v>7</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT17" t="n">
         <v>17.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ17" t="n">
         <v>11.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G18" t="n">
         <v>1.68</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
         <v>7</v>
@@ -4936,10 +4936,10 @@
         <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4963,22 +4963,22 @@
         <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="n">
         <v>350</v>
@@ -4987,31 +4987,31 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
         <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
@@ -5023,19 +5023,19 @@
         <v>700</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS18" t="n">
         <v>11</v>
@@ -5044,13 +5044,13 @@
         <v>5.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV18" t="n">
         <v>19.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX18" t="n">
         <v>7.4</v>
@@ -5062,7 +5062,7 @@
         <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5071,7 +5071,7 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE18" t="n">
         <v>11</v>
@@ -5083,22 +5083,22 @@
         <v>11</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BN18" t="n">
         <v>4.1</v>
@@ -5110,41 +5110,41 @@
         <v>12</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT18" t="n">
         <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BZ18" t="n">
         <v>27</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5175,31 +5175,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H19" t="n">
         <v>13.5</v>
       </c>
       <c r="I19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
         <v>1.31</v>
@@ -5208,197 +5208,197 @@
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z19" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE19" t="n">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="AF19" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AI19" t="n">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="AJ19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
         <v>65</v>
       </c>
       <c r="AM19" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV19" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
         <v>50</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF19" t="n">
         <v>5.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BJ19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BN19" t="n">
         <v>3.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BP19" t="n">
         <v>7.4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT19" t="n">
         <v>19.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5429,52 +5429,52 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G20" t="n">
         <v>1.49</v>
       </c>
       <c r="H20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K20" t="n">
         <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
@@ -5483,40 +5483,40 @@
         <v>3</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="n">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="AD20" t="n">
         <v>40</v>
       </c>
       <c r="AE20" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AF20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AI20" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ20" t="n">
         <v>12.5</v>
@@ -5531,76 +5531,76 @@
         <v>310</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO20" t="n">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="AP20" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>21</v>
       </c>
       <c r="AR20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB20" t="n">
         <v>11</v>
       </c>
-      <c r="AS20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BC20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
         <v>44</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BH20" t="n">
         <v>3.25</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ20" t="n">
         <v>13.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,13 +5612,13 @@
         <v>3.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="BP20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
@@ -5627,7 +5627,7 @@
         <v>11</v>
       </c>
       <c r="BT20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BU20" t="n">
         <v>7.2</v>
@@ -5636,13 +5636,13 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ20" t="n">
         <v>21</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,52 +857,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.9</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.6</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.51</v>
@@ -914,118 +914,118 @@
         <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>370</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT2" t="n">
         <v>10</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>15</v>
       </c>
       <c r="BA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
         <v>8</v>
@@ -1034,43 +1034,43 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
         <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>5.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1114,227 +1114,227 @@
         <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
         <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BA3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="H4" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
@@ -1395,70 +1395,70 @@
         <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE4" t="n">
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ4" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AL4" t="n">
         <v>370</v>
@@ -1476,7 +1476,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
         <v>11.5</v>
@@ -1485,7 +1485,7 @@
         <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
         <v>6.4</v>
@@ -1494,40 +1494,40 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BA4" t="n">
         <v>23</v>
       </c>
       <c r="BB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE4" t="n">
         <v>11</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI4" t="n">
         <v>2.58</v>
@@ -1536,49 +1536,49 @@
         <v>11</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>11</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1619,154 +1619,154 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
         <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
         <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
         <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AA5" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="AB5" t="n">
         <v>6.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
         <v>160</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AK5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL5" t="n">
         <v>60</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AS5" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT5" t="n">
         <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BA5" t="n">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
         <v>27</v>
@@ -1775,19 +1775,19 @@
         <v>17.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="BK5" t="n">
         <v>6.6</v>
@@ -1796,19 +1796,19 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO5" t="n">
         <v>3.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,10 +1817,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.46</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G6" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.56</v>
@@ -1897,13 +1897,13 @@
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
         <v>2.56</v>
@@ -1912,31 +1912,31 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="X6" t="n">
         <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
         <v>8.199999999999999</v>
@@ -1945,7 +1945,7 @@
         <v>7</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE6" t="n">
         <v>60</v>
@@ -1954,28 +1954,28 @@
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="AJ6" t="n">
         <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
@@ -1987,10 +1987,10 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>7.2</v>
@@ -1999,10 +1999,10 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AX6" t="n">
         <v>12</v>
@@ -2011,34 +2011,34 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
         <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="n">
         <v>2.78</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6" t="n">
         <v>11</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5</v>
@@ -2059,7 +2059,7 @@
         <v>4.5</v>
       </c>
       <c r="BP6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ6" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
         <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT6" t="n">
         <v>6.6</v>
@@ -2086,17 +2086,17 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>44</v>
       </c>
       <c r="CA6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2130,49 +2130,49 @@
         <v>3.15</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
         <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="P7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R7" t="n">
         <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
         <v>1.47</v>
@@ -2181,76 +2181,76 @@
         <v>1.43</v>
       </c>
       <c r="X7" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AJ7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK7" t="n">
         <v>70</v>
       </c>
-      <c r="AK7" t="n">
-        <v>60</v>
-      </c>
       <c r="AL7" t="n">
-        <v>200</v>
+        <v>460</v>
       </c>
       <c r="AM7" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
-        <v>230</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="n">
         <v>7.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AV7" t="n">
         <v>13</v>
@@ -2259,37 +2259,37 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY7" t="n">
         <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
       </c>
       <c r="BD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG7" t="n">
         <v>11</v>
       </c>
-      <c r="BE7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH7" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BI7" t="n">
         <v>2.18</v>
@@ -2298,13 +2298,13 @@
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,13 +2316,13 @@
         <v>32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT7" t="n">
         <v>5.8</v>
@@ -2334,23 +2334,23 @@
         <v>29</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
         <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.78</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.96</v>
       </c>
       <c r="H8" t="n">
         <v>3.2</v>
@@ -2393,31 +2393,31 @@
         <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="M8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
@@ -2426,31 +2426,31 @@
         <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
         <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD8" t="n">
         <v>16</v>
@@ -2459,10 +2459,10 @@
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
@@ -2471,112 +2471,112 @@
         <v>460</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY8" t="n">
         <v>12</v>
       </c>
-      <c r="AW8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BB8" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF8" t="n">
         <v>36</v>
       </c>
-      <c r="BF8" t="n">
-        <v>9</v>
-      </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BH8" t="n">
         <v>2.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN8" t="n">
         <v>5.7</v>
       </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BO8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>6.2</v>
@@ -2585,26 +2585,26 @@
         <v>4.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="G9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.6</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>1.42</v>
@@ -2659,160 +2659,160 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
         <v>160</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AL9" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>13</v>
       </c>
-      <c r="AS9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB9" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BC9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BG9" t="n">
         <v>15</v>
       </c>
-      <c r="BD9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN9" t="n">
         <v>6.6</v>
@@ -2824,7 +2824,7 @@
         <v>28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>40</v>
@@ -2842,23 +2842,23 @@
         <v>17.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX9" t="n">
         <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AJ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK10" t="n">
         <v>21</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
       </c>
       <c r="AL10" t="n">
         <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
         <v>36</v>
       </c>
       <c r="BE10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF10" t="n">
         <v>11</v>
       </c>
-      <c r="BF10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BG10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>11</v>
       </c>
-      <c r="BH10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BN10" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="BP10" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>6</v>
       </c>
       <c r="BR10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>1.44</v>
@@ -3167,7 +3167,7 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
@@ -3176,7 +3176,7 @@
         <v>1.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
@@ -3185,46 +3185,46 @@
         <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
@@ -3233,10 +3233,10 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -3245,25 +3245,25 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
         <v>6.8</v>
@@ -3272,88 +3272,88 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BT11" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BW11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BY11" t="n">
         <v>10.5</v>
@@ -3362,11 +3362,11 @@
         <v>32</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3397,79 +3397,79 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="I12" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.58</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.54</v>
-      </c>
       <c r="U12" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="Y12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="n">
         <v>38</v>
       </c>
       <c r="AA12" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
         <v>34</v>
@@ -3478,61 +3478,61 @@
         <v>90</v>
       </c>
       <c r="AG12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AH12" t="n">
         <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AK12" t="n">
         <v>80</v>
       </c>
       <c r="AL12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>970</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP12" t="n">
         <v>11</v>
       </c>
-      <c r="AP12" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
         <v>12</v>
@@ -3541,10 +3541,10 @@
         <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BD12" t="n">
         <v>13.5</v>
@@ -3553,13 +3553,13 @@
         <v>10.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BI12" t="n">
         <v>3.4</v>
@@ -3568,16 +3568,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO12" t="n">
         <v>6</v>
@@ -3586,41 +3586,41 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU12" t="n">
         <v>4.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
         <v>2.84</v>
       </c>
       <c r="I13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -3681,34 +3681,34 @@
         <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R13" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
         <v>1.43</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V13" t="n">
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X13" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Y13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
         <v>30</v>
@@ -3717,7 +3717,7 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC13" t="n">
         <v>14.5</v>
@@ -3726,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF13" t="n">
         <v>25</v>
@@ -3738,25 +3738,25 @@
         <v>17.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="n">
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AO13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP13" t="n">
         <v>19</v>
@@ -3765,13 +3765,13 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU13" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AX13" t="n">
         <v>19</v>
@@ -3792,7 +3792,7 @@
         <v>12.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
         <v>16.5</v>
@@ -3801,19 +3801,19 @@
         <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
         <v>10.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BI13" t="n">
         <v>4.2</v>
@@ -3822,13 +3822,13 @@
         <v>8.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN13" t="n">
         <v>6.2</v>
@@ -3840,16 +3840,16 @@
         <v>14.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU13" t="n">
         <v>5.3</v>
@@ -3858,23 +3858,23 @@
         <v>18.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3905,130 +3905,130 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="G14" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="I14" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
         <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AF14" t="n">
         <v>24</v>
       </c>
       <c r="AG14" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="AK14" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
         <v>9.199999999999999</v>
@@ -4043,92 +4043,92 @@
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BC14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
         <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO14" t="n">
         <v>5</v>
       </c>
       <c r="BP14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BQ14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT14" t="n">
         <v>5.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="CA14" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
         <v>7.4</v>
@@ -4174,49 +4174,49 @@
         <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z15" t="n">
         <v>160</v>
@@ -4225,7 +4225,7 @@
         <v>220</v>
       </c>
       <c r="AB15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15" t="n">
         <v>42</v>
@@ -4237,22 +4237,22 @@
         <v>200</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>42</v>
       </c>
       <c r="AI15" t="n">
         <v>240</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
         <v>150</v>
@@ -4273,10 +4273,10 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -4288,43 +4288,43 @@
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX15" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC15" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC15" t="n">
-        <v>9</v>
-      </c>
       <c r="BD15" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
         <v>11</v>
@@ -4375,14 +4375,14 @@
         <v>10</v>
       </c>
       <c r="BZ15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
         <v>7.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4413,61 +4413,61 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T16" t="n">
         <v>1.6</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.54</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
         <v>970</v>
@@ -4479,10 +4479,10 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>970</v>
@@ -4506,43 +4506,43 @@
         <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="AO16" t="n">
         <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -4551,46 +4551,46 @@
         <v>5.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="BD16" t="n">
         <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>11.5</v>
+        <v>2.58</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
@@ -4602,41 +4602,41 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BU16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.25</v>
+        <v>2.42</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4673,16 +4673,16 @@
         <v>1.27</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -4694,13 +4694,13 @@
         <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
         <v>1.53</v>
@@ -4709,10 +4709,10 @@
         <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
         <v>1.06</v>
@@ -4721,7 +4721,7 @@
         <v>4.7</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y17" t="n">
         <v>44</v>
@@ -4730,40 +4730,40 @@
         <v>160</v>
       </c>
       <c r="AA17" t="n">
-        <v>800</v>
+        <v>860</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AD17" t="n">
         <v>50</v>
       </c>
       <c r="AE17" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AF17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI17" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
         <v>260</v>
@@ -4772,46 +4772,46 @@
         <v>5.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="AP17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ17" t="n">
         <v>38</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AS17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
@@ -4820,10 +4820,10 @@
         <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
         <v>15</v>
@@ -4835,7 +4835,7 @@
         <v>3.45</v>
       </c>
       <c r="BJ17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK17" t="n">
         <v>6.8</v>
@@ -4844,28 +4844,28 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BP17" t="n">
         <v>7</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BU17" t="n">
         <v>7.4</v>
@@ -4874,13 +4874,13 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ17" t="n">
         <v>11.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
         <v>6.4</v>
@@ -4933,10 +4933,10 @@
         <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.52</v>
@@ -4945,40 +4945,40 @@
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="V18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z18" t="n">
         <v>350</v>
@@ -4987,10 +4987,10 @@
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
         <v>75</v>
@@ -4999,7 +4999,7 @@
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -5011,7 +5011,7 @@
         <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
@@ -5023,7 +5023,7 @@
         <v>700</v>
       </c>
       <c r="AN18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
@@ -5032,13 +5032,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
         <v>5.8</v>
@@ -5047,22 +5047,22 @@
         <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -5071,22 +5071,22 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BE18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
@@ -5101,28 +5101,28 @@
         <v>13</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5137,14 +5137,14 @@
         <v>12</v>
       </c>
       <c r="BZ18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="G19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H19" t="n">
         <v>13.5</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
         <v>6.2</v>
@@ -5193,148 +5193,148 @@
         <v>6.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z19" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE19" t="n">
-        <v>490</v>
+        <v>360</v>
       </c>
       <c r="AF19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AI19" t="n">
-        <v>410</v>
+        <v>270</v>
       </c>
       <c r="AJ19" t="n">
         <v>9</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>430</v>
+        <v>330</v>
       </c>
       <c r="AN19" t="n">
         <v>6.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>860</v>
+        <v>690</v>
       </c>
       <c r="AP19" t="n">
         <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BH19" t="n">
         <v>3.75</v>
@@ -5343,22 +5343,22 @@
         <v>2.98</v>
       </c>
       <c r="BJ19" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BO19" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="BP19" t="n">
         <v>7.4</v>
@@ -5370,35 +5370,35 @@
         <v>32</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ19" t="n">
         <v>14</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L20" t="n">
         <v>1.47</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.46</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
@@ -5459,97 +5459,97 @@
         <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U20" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
         <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AA20" t="n">
-        <v>440</v>
+        <v>540</v>
       </c>
       <c r="AB20" t="n">
         <v>6.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE20" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AF20" t="n">
         <v>7.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI20" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AJ20" t="n">
         <v>12.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
         <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AN20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>410</v>
+      </c>
+      <c r="AP20" t="n">
         <v>11</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>360</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU20" t="n">
         <v>9.6</v>
@@ -5558,76 +5558,76 @@
         <v>30</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY20" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BB20" t="n">
         <v>11</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
         <v>44</v>
       </c>
       <c r="BE20" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="n">
         <v>3.25</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT20" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>12.5</v>
       </c>
       <c r="BU20" t="n">
         <v>7.2</v>
@@ -5636,23 +5636,23 @@
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BZ20" t="n">
         <v>21</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.86</v>
+        <v>20</v>
       </c>
       <c r="H2" t="n">
-        <v>2.74</v>
+        <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>1.41</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>2.56</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>3.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA2" t="n">
         <v>11</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>36</v>
-      </c>
       <c r="BB2" t="n">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>26</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="BF2" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="BG2" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="AC3" t="n">
         <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AI3" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>130</v>
+        <v>550</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AO3" t="n">
-        <v>600</v>
+        <v>390</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS3" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="BD3" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.4</v>
+        <v>320</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.88</v>
+        <v>1.82</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.54</v>
+        <v>1.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>860</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>95</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.800000000000001</v>
+        <v>130</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -1365,220 +1365,220 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AN4" t="n">
         <v>160</v>
       </c>
-      <c r="AL4" t="n">
-        <v>370</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>600</v>
-      </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BB4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BD4" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BE4" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>150</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>11</v>
       </c>
-      <c r="BF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>10</v>
-      </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BU4" t="n">
         <v>4.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.62</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.64</v>
-      </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
         <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X5" t="n">
         <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="AA5" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC5" t="n">
         <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AE5" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AI5" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS5" t="n">
         <v>14</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13.5</v>
       </c>
       <c r="AT5" t="n">
         <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA5" t="n">
         <v>36</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BE5" t="n">
-        <v>17.5</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>65</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP5" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU5" t="n">
         <v>6.4</v>
       </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6</v>
-      </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -1873,169 +1873,169 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
         <v>1.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
         <v>5.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>9.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC6" t="n">
         <v>7</v>
       </c>
       <c r="AD6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14</v>
-      </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
         <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
         <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BD6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BE6" t="n">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BG6" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BI6" t="n">
         <v>2.42</v>
@@ -2044,59 +2044,59 @@
         <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>17.5</v>
+        <v>170</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BW6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY6" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>14.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>44</v>
       </c>
       <c r="CA6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -2127,106 +2127,106 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="L7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="M7" t="n">
         <v>1.17</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="AJ7" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AL7" t="n">
         <v>460</v>
       </c>
       <c r="AM7" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
         <v>600</v>
@@ -2235,122 +2235,122 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AY7" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>1.96</v>
       </c>
       <c r="BB7" t="n">
-        <v>25</v>
+        <v>1.95</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>1.95</v>
       </c>
       <c r="BD7" t="n">
-        <v>11.5</v>
+        <v>1.96</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.5</v>
+        <v>200</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>1.96</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>1.97</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14.5</v>
+        <v>250</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K8" t="n">
         <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
         <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
         <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z8" t="n">
         <v>20</v>
@@ -2447,49 +2447,49 @@
         <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
         <v>7</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>460</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
         <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
         <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
         <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>8.4</v>
@@ -2498,7 +2498,7 @@
         <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2510,7 +2510,7 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -2522,89 +2522,89 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BB8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD8" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BE8" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="BF8" t="n">
         <v>36</v>
       </c>
       <c r="BG8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.5</v>
+        <v>200</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
         <v>27</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>3.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J9" t="n">
         <v>3.6</v>
@@ -2659,40 +2659,40 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z9" t="n">
         <v>14</v>
@@ -2704,7 +2704,7 @@
         <v>15</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>11</v>
@@ -2713,31 +2713,31 @@
         <v>24</v>
       </c>
       <c r="AF9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG9" t="n">
         <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AK9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
         <v>18.5</v>
@@ -2746,7 +2746,7 @@
         <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>11.5</v>
@@ -2755,46 +2755,46 @@
         <v>19.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY9" t="n">
         <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
         <v>24</v>
       </c>
       <c r="BB9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF9" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.4</v>
@@ -2803,62 +2803,62 @@
         <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>13.5</v>
+        <v>100</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP9" t="n">
         <v>28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR9" t="n">
         <v>40</v>
       </c>
       <c r="BS9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT9" t="n">
         <v>5.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV9" t="n">
         <v>17.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX9" t="n">
         <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -2889,25 +2889,25 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.68</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.73</v>
       </c>
       <c r="H10" t="n">
         <v>5.9</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2919,7 +2919,7 @@
         <v>1.39</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q10" t="n">
         <v>2.16</v>
@@ -2934,55 +2934,55 @@
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="X10" t="n">
         <v>13</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
         <v>260</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>46</v>
@@ -2991,28 +2991,28 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>190</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>16.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
         <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
         <v>21</v>
@@ -3030,67 +3030,67 @@
         <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="BD10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>42</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="BN10" t="n">
         <v>4.1</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3105,14 +3105,14 @@
         <v>10</v>
       </c>
       <c r="BZ10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -3143,85 +3143,85 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.15</v>
       </c>
-      <c r="I11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
         <v>1.36</v>
       </c>
       <c r="P11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.84</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -3230,13 +3230,13 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -3245,73 +3245,73 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="AT11" t="n">
         <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
         <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC11" t="n">
         <v>22</v>
       </c>
-      <c r="BC11" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE11" t="n">
         <v>9.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11" t="n">
         <v>5.8</v>
@@ -3320,16 +3320,16 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ11" t="n">
         <v>8</v>
@@ -3338,22 +3338,22 @@
         <v>34</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
         <v>10.5</v>
@@ -3362,11 +3362,11 @@
         <v>32</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -3397,61 +3397,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="U12" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W12" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
         <v>34</v>
@@ -3463,7 +3463,7 @@
         <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC12" t="n">
         <v>14</v>
@@ -3472,7 +3472,7 @@
         <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
         <v>90</v>
@@ -3487,7 +3487,7 @@
         <v>500</v>
       </c>
       <c r="AJ12" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="AK12" t="n">
         <v>80</v>
@@ -3499,16 +3499,16 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
         <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
         <v>9.199999999999999</v>
@@ -3520,13 +3520,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV12" t="n">
         <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>16.5</v>
@@ -3541,31 +3541,31 @@
         <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD12" t="n">
         <v>13.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BI12" t="n">
         <v>3.4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK12" t="n">
         <v>5.7</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN12" t="n">
         <v>6.8</v>
@@ -3586,7 +3586,7 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3595,7 +3595,7 @@
         <v>10.5</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BU12" t="n">
         <v>4.7</v>
@@ -3613,14 +3613,14 @@
         <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
         <v>2.84</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J13" t="n">
         <v>4.2</v>
@@ -3687,25 +3687,25 @@
         <v>1.41</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S13" t="n">
         <v>2.04</v>
       </c>
       <c r="T13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="U13" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y13" t="n">
         <v>24</v>
@@ -3717,13 +3717,13 @@
         <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE13" t="n">
         <v>30</v>
@@ -3738,64 +3738,64 @@
         <v>17.5</v>
       </c>
       <c r="AI13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL13" t="n">
         <v>32</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>30</v>
       </c>
       <c r="AM13" t="n">
         <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AQ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS13" t="n">
         <v>20</v>
       </c>
-      <c r="AR13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>21</v>
-      </c>
       <c r="AT13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU13" t="n">
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
         <v>18.5</v>
@@ -3804,77 +3804,77 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
         <v>10.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BI13" t="n">
         <v>4.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
         <v>6.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP13" t="n">
         <v>14.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR13" t="n">
         <v>19.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>6.8</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV13" t="n">
         <v>18.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I14" t="n">
         <v>2.52</v>
@@ -3920,79 +3920,79 @@
         <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD14" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF14" t="n">
         <v>24</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
         <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="n">
         <v>440</v>
@@ -4001,31 +4001,31 @@
         <v>100</v>
       </c>
       <c r="AL14" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
         <v>29</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR14" t="n">
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -4034,10 +4034,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
@@ -4046,7 +4046,7 @@
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
         <v>23</v>
@@ -4055,52 +4055,52 @@
         <v>18.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>18</v>
+        <v>9.6</v>
       </c>
       <c r="BG14" t="n">
         <v>21</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="BJ14" t="n">
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN14" t="n">
         <v>6.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP14" t="n">
         <v>30</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR14" t="n">
         <v>46</v>
       </c>
       <c r="BS14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT14" t="n">
         <v>5.4</v>
@@ -4112,23 +4112,23 @@
         <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX14" t="n">
         <v>38</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>36</v>
       </c>
       <c r="CA14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G15" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -4183,61 +4183,61 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
         <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="X15" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z15" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>16.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
@@ -4246,52 +4246,52 @@
         <v>42</v>
       </c>
       <c r="AI15" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AJ15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL15" t="n">
         <v>150</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO15" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AP15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
         <v>8.800000000000001</v>
@@ -4300,89 +4300,89 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC15" t="n">
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15" t="n">
         <v>11</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO15" t="n">
         <v>3.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT15" t="n">
         <v>10.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -4425,46 +4425,46 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
         <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
         <v>40</v>
@@ -4479,13 +4479,13 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AE16" t="n">
         <v>120</v>
@@ -4494,22 +4494,22 @@
         <v>24</v>
       </c>
       <c r="AG16" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AI16" t="n">
         <v>150</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
@@ -4521,67 +4521,67 @@
         <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
         <v>14.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BK16" t="n">
         <v>5.6</v>
@@ -4590,53 +4590,53 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.58</v>
+        <v>11.5</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT16" t="n">
         <v>7.8</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>1.26</v>
       </c>
       <c r="G17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K17" t="n">
         <v>6.8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -4691,61 +4691,61 @@
         <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T17" t="n">
         <v>2.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
         <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="X17" t="n">
         <v>26</v>
       </c>
       <c r="Y17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z17" t="n">
         <v>160</v>
       </c>
       <c r="AA17" t="n">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>15</v>
       </c>
       <c r="AD17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AE17" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AF17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
@@ -4754,25 +4754,25 @@
         <v>38</v>
       </c>
       <c r="AI17" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ17" t="n">
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
         <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -4781,37 +4781,37 @@
         <v>38</v>
       </c>
       <c r="AR17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS17" t="n">
         <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU17" t="n">
         <v>13.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AW17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA17" t="n">
         <v>14.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC17" t="n">
         <v>13</v>
@@ -4820,34 +4820,34 @@
         <v>38</v>
       </c>
       <c r="BE17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
         <v>15</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BJ17" t="n">
         <v>14</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BO17" t="n">
         <v>3.2</v>
@@ -4856,41 +4856,41 @@
         <v>7</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR17" t="n">
         <v>26</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA17" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I18" t="n">
         <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.52</v>
@@ -4951,7 +4951,7 @@
         <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
         <v>2.32</v>
@@ -4960,19 +4960,19 @@
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
         <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X18" t="n">
         <v>11</v>
@@ -4981,133 +4981,133 @@
         <v>18.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>240</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>380</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
         <v>700</v>
       </c>
       <c r="AN18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB18" t="n">
         <v>14</v>
       </c>
-      <c r="AO18" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB18" t="n">
+      <c r="BC18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF18" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>10</v>
-      </c>
       <c r="BG18" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ18" t="n">
         <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ18" t="n">
         <v>6.6</v>
@@ -5116,35 +5116,35 @@
         <v>34</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ18" t="n">
         <v>28</v>
       </c>
       <c r="CA18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -5175,61 +5175,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="H19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="J19" t="n">
         <v>6.2</v>
       </c>
       <c r="K19" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V19" t="n">
         <v>1.07</v>
       </c>
       <c r="W19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
         <v>36</v>
@@ -5238,25 +5238,25 @@
         <v>150</v>
       </c>
       <c r="AA19" t="n">
-        <v>990</v>
+        <v>920</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD19" t="n">
         <v>60</v>
       </c>
       <c r="AE19" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AF19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
         <v>44</v>
@@ -5271,55 +5271,55 @@
         <v>21</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AP19" t="n">
         <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS19" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA19" t="n">
         <v>11</v>
       </c>
-      <c r="BA19" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BB19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
@@ -5328,77 +5328,77 @@
         <v>48</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BJ19" t="n">
         <v>15.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BN19" t="n">
         <v>3.55</v>
       </c>
       <c r="BO19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR19" t="n">
         <v>32</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT19" t="n">
         <v>17.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G20" t="n">
         <v>1.48</v>
       </c>
       <c r="H20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.47</v>
@@ -5453,25 +5453,25 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q20" t="n">
         <v>2.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
         <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
         <v>1.61</v>
@@ -5489,10 +5489,10 @@
         <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA20" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
         <v>6.4</v>
@@ -5501,13 +5501,13 @@
         <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE20" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG20" t="n">
         <v>11</v>
@@ -5522,7 +5522,7 @@
         <v>12.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AL20" t="n">
         <v>60</v>
@@ -5543,13 +5543,13 @@
         <v>21</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AS20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU20" t="n">
         <v>9.6</v>
@@ -5558,10 +5558,10 @@
         <v>30</v>
       </c>
       <c r="AW20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY20" t="n">
         <v>9.6</v>
@@ -5570,43 +5570,43 @@
         <v>30</v>
       </c>
       <c r="BA20" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB20" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>11</v>
       </c>
       <c r="BC20" t="n">
         <v>16.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF20" t="n">
         <v>9</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ20" t="n">
         <v>14</v>
       </c>
       <c r="BK20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>15</v>
+        <v>2.9</v>
       </c>
       <c r="BN20" t="n">
         <v>3.55</v>
@@ -5615,44 +5615,44 @@
         <v>3.2</v>
       </c>
       <c r="BP20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR20" t="n">
         <v>34</v>
       </c>
       <c r="BS20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT20" t="n">
         <v>13.5</v>
       </c>
       <c r="BU20" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>21</v>
       </c>
       <c r="CA20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 06:09:21</t>
+          <t>2026-05-28 08:24:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,180 +843,180 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Wieczysta Krakow</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.41</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.44</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>1.88</v>
       </c>
       <c r="K2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>980</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>25</v>
-      </c>
       <c r="BB2" t="n">
-        <v>220</v>
+        <v>15.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 14:47:37</t>
+          <t>2026-05-28 17:08:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="G3" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN3" t="n">
         <v>4.3</v>
       </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AO3" t="n">
+        <v>560</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG3" t="n">
         <v>17</v>
       </c>
-      <c r="AE3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
+      <c r="BH3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>14</v>
       </c>
-      <c r="BA3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9</v>
-      </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BS3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BU3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BU3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BV3" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="BY3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>10</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 14:47:37</t>
+          <t>2026-05-28 17:08:06</t>
         </is>
       </c>
     </row>
@@ -1356,187 +1356,187 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="G4" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN4" t="n">
         <v>15.5</v>
       </c>
-      <c r="I4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5</v>
-      </c>
-      <c r="X4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AO4" t="n">
         <v>220</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL4" t="n">
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS4" t="n">
         <v>42</v>
       </c>
-      <c r="AM4" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD4" t="n">
         <v>44</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>38</v>
       </c>
       <c r="BE4" t="n">
         <v>130</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>170</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>6.8</v>
       </c>
-      <c r="BQ4" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BR4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="BU4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="BW4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX4" t="n">
-        <v>120</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>5.3</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 14:47:37</t>
+          <t>2026-05-28 17:08:06</t>
         </is>
       </c>
     </row>
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>990</v>
+      </c>
+      <c r="AB5" t="n">
         <v>6.8</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="X5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>360</v>
+      </c>
+      <c r="AF5" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>280</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>750</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB5" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="BC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BU5" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN5" t="n">
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO5" t="n">
-        <v>190</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="CA5" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>170</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>75</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>29</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>10</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 14:47:37</t>
+          <t>2026-05-28 17:08:06</t>
         </is>
       </c>
     </row>
@@ -1864,493 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.3</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="S6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X6" t="n">
         <v>13</v>
       </c>
-      <c r="I6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>18</v>
-      </c>
       <c r="Y6" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AA6" t="n">
-        <v>830</v>
+        <v>350</v>
       </c>
       <c r="AB6" t="n">
         <v>6.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>410</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN6" t="n">
         <v>11</v>
       </c>
-      <c r="AH6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI6" t="n">
+      <c r="AO6" t="n">
         <v>270</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>630</v>
-      </c>
       <c r="AP6" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AS6" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE6" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG6" t="n">
         <v>16</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BJ6" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ6" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 14:47:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Boca Juniors</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Univ Catolica (Chile)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X7" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>17</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>10</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-05-28 14:47:37</t>
+          <t>2026-05-28 17:08:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.5</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>60</v>
       </c>
       <c r="J2" t="n">
-        <v>1.88</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.89</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,34 +881,34 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.17</v>
+        <v>10</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -923,46 +923,46 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO2" t="n">
         <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>17.5</v>
       </c>
       <c r="AP2" t="n">
         <v>1000</v>
@@ -977,110 +977,110 @@
         <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.5</v>
+        <v>80</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>290</v>
       </c>
       <c r="AX2" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.08</v>
+        <v>32</v>
       </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>160</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.5</v>
+        <v>150</v>
       </c>
       <c r="BF2" t="n">
-        <v>26</v>
+        <v>3.35</v>
       </c>
       <c r="BG2" t="n">
-        <v>14</v>
+        <v>300</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:08:06</t>
+          <t>2026-05-28 19:29:09</t>
         </is>
       </c>
     </row>
@@ -1102,239 +1102,239 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC3" t="n">
         <v>7.6</v>
       </c>
-      <c r="K3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AD3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK3" t="n">
         <v>29</v>
       </c>
-      <c r="Y3" t="n">
-        <v>65</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>340</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX3" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>560</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="BB3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>240</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>800</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU3" t="n">
         <v>8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>170</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BV3" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>70</v>
       </c>
       <c r="BX3" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="BZ3" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.8</v>
+        <v>60</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:08:06</t>
+          <t>2026-05-28 19:29:09</t>
         </is>
       </c>
     </row>
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="H4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K4" t="n">
         <v>6.4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>880</v>
+      </c>
+      <c r="AB4" t="n">
         <v>6.6</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>450</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>680</v>
+      </c>
+      <c r="AP4" t="n">
         <v>17</v>
       </c>
-      <c r="Z4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AQ4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB4" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
         <v>15</v>
       </c>
-      <c r="BC4" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE4" t="n">
         <v>130</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BK4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BN4" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BV4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BX4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:08:06</t>
+          <t>2026-05-28 19:29:09</t>
         </is>
       </c>
     </row>
@@ -1610,493 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="G5" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="H5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X5" t="n">
         <v>14</v>
       </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK5" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>990</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>360</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AG5" t="n">
+      <c r="AL5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN5" t="n">
         <v>11</v>
       </c>
-      <c r="AH5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>280</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AO5" t="n">
-        <v>750</v>
+        <v>270</v>
       </c>
       <c r="AP5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS5" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>16</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AW5" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="BA5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>95</v>
+      </c>
+      <c r="BW5" t="n">
         <v>16</v>
       </c>
-      <c r="BN5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BS5" t="n">
+      <c r="BX5" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA5" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:08:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Boca Juniors</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Univ Catolica (Chile)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-05-28 17:08:06</t>
+          <t>2026-05-28 19:29:09</t>
         </is>
       </c>
     </row>
